--- a/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>HLLY</t>
   </si>
@@ -656,80 +656,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45200</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45109</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45018</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44836</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44745</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44654</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44465</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44374</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44283</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43918</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -739,109 +740,115 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>155700</v>
+      </c>
+      <c r="E8" s="3">
         <v>156500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>175300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>172200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>154200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>154800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>179400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>200100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>179800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>159700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>193000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>160300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>138400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>107200</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S8" s="3">
-        <v>0</v>
+      <c r="S8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>95500</v>
+      </c>
+      <c r="E9" s="3">
         <v>98200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>105500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>104500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>106900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>106400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>104100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>117300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>105100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>94500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>111800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>94700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>83900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>63800</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -851,53 +858,56 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E10" s="3">
         <v>58300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>69800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>67700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>47300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>48400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>75300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>82800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>74700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>65200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>81200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>65600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>54500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>43400</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -907,8 +917,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -929,53 +942,54 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E12" s="3">
         <v>6100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6200</v>
-      </c>
-      <c r="F12" s="3">
-        <v>6700</v>
       </c>
       <c r="G12" s="3">
         <v>6700</v>
       </c>
       <c r="H12" s="3">
+        <v>6700</v>
+      </c>
+      <c r="I12" s="3">
         <v>6000</v>
-      </c>
-      <c r="I12" s="3">
-        <v>8200</v>
       </c>
       <c r="J12" s="3">
         <v>8200</v>
       </c>
       <c r="K12" s="3">
+        <v>8200</v>
+      </c>
+      <c r="L12" s="3">
         <v>8100</v>
-      </c>
-      <c r="L12" s="3">
-        <v>7100</v>
       </c>
       <c r="M12" s="3">
         <v>7100</v>
       </c>
       <c r="N12" s="3">
+        <v>7100</v>
+      </c>
+      <c r="O12" s="3">
         <v>6000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>6300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5600</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -985,8 +999,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1041,53 +1058,56 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>400</v>
+        <v>-200</v>
       </c>
       <c r="E14" s="3">
         <v>400</v>
       </c>
       <c r="F14" s="3">
-        <v>1300</v>
+        <v>400</v>
       </c>
       <c r="G14" s="3">
         <v>1300</v>
       </c>
       <c r="H14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="I14" s="3">
         <v>3700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>14000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>25000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>19700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>7500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1097,13 +1117,16 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>3700</v>
+        <v>3500</v>
       </c>
       <c r="E15" s="3">
         <v>3700</v>
@@ -1124,37 +1147,40 @@
         <v>3700</v>
       </c>
       <c r="K15" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="L15" s="3">
         <v>3600</v>
       </c>
       <c r="M15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="N15" s="3">
         <v>3500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2700</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1172,53 +1198,54 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>136200</v>
+      </c>
+      <c r="E17" s="3">
         <v>137200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>145300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>146200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>167700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>151700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>154300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>164000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>169300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>159200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>153000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>147600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>125400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>89500</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1228,53 +1255,56 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E18" s="3">
         <v>19300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>30000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>26000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-13500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>25100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>36100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>40000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>17700</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1284,8 +1314,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1306,41 +1339,42 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>7300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>37600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>27400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-17300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-24200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1350,8 +1384,8 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1362,53 +1396,56 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E21" s="3">
         <v>23000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>33100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>30300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>47200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>58700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>37200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>45800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>18400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>17900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>22400</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1418,109 +1455,115 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E22" s="3">
         <v>13700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>18300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>13400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>10400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>11200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>10100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11500</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E23" s="3">
         <v>2800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>17100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-19600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>30200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>43600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>24000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-33500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>28900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6200</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1530,64 +1573,70 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>2100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-4400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1300</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1642,53 +1691,56 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E26" s="3">
         <v>800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-15200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>31600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>40600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>16900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-18000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-30200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>23100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4900</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,53 +1750,56 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E27" s="3">
         <v>800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>13000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-15200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>31600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>40600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-18000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-30200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>23100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4900</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1754,8 +1809,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1810,8 +1868,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1866,8 +1927,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1922,8 +1986,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1978,41 +2045,44 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E32" s="3">
         <v>2700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-7300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-37600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-27400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>17300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>24200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2022,8 +2092,8 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -2034,53 +2104,56 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E33" s="3">
         <v>800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>13000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-15200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>31600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>40600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-18000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-30200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>23100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4900</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2090,8 +2163,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2146,53 +2222,56 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E35" s="3">
         <v>800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>13000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-15200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>31600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>40600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-18000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-30200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>23100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4900</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2202,58 +2281,61 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45200</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45109</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45018</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44836</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44745</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44654</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44465</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44374</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44283</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43918</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2263,8 +2345,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2285,8 +2370,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2307,41 +2393,42 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E41" s="3">
         <v>36800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>42700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>26200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>44100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>53900</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2363,8 +2450,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2419,41 +2509,44 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E43" s="3">
         <v>47400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>57100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>56300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>47100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>59700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>58200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>63700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>51400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>55400</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2469,47 +2562,50 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
+      <c r="S43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>192300</v>
+      </c>
+      <c r="E44" s="3">
         <v>207200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>217500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>229000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>233600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>230500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>214900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>191100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>185000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>164300</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2525,47 +2621,50 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E45" s="3">
         <v>13300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>18200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>18500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>16900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>19000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8900</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2587,41 +2686,44 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>297400</v>
+      </c>
+      <c r="E46" s="3">
         <v>304700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>333300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>324200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>325000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>325300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>320500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>314300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>291700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>282600</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2643,8 +2745,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2690,8 +2795,8 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>0</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
@@ -2699,41 +2804,44 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>76500</v>
+      </c>
+      <c r="E48" s="3">
         <v>78400</v>
-      </c>
-      <c r="E48" s="3">
-        <v>78700</v>
       </c>
       <c r="F48" s="3">
         <v>78700</v>
       </c>
       <c r="G48" s="3">
+        <v>78700</v>
+      </c>
+      <c r="H48" s="3">
         <v>81700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>86000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>88800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>88000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>51500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>50400</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2749,47 +2857,50 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S48" s="3">
-        <v>0</v>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>829500</v>
+      </c>
+      <c r="E49" s="3">
         <v>832800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>836700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>839400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>843000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>845700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>851500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>846400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>849800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>803700</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2805,14 +2916,17 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2867,8 +2981,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2923,20 +3040,23 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3">
         <v>3200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>2100</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2952,8 +3072,8 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -2979,8 +3099,11 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3035,41 +3158,44 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1203300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1219100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1250700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1242300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1249600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1257100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1260800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1248700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1193100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1136700</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3091,8 +3217,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3113,8 +3242,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3135,41 +3265,42 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E57" s="3">
         <v>39800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>43800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>37400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>44900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>43500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>39600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>41900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>45700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>46600</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3185,19 +3316,22 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6600</v>
+        <v>7500</v>
       </c>
       <c r="E58" s="3">
         <v>6600</v>
@@ -3206,26 +3340,26 @@
         <v>6600</v>
       </c>
       <c r="G58" s="3">
+        <v>6600</v>
+      </c>
+      <c r="H58" s="3">
         <v>7000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>6300</v>
       </c>
       <c r="J58" s="3">
         <v>6300</v>
       </c>
       <c r="K58" s="3">
+        <v>6300</v>
+      </c>
+      <c r="L58" s="3">
         <v>7900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5500</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3247,41 +3381,44 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E59" s="3">
         <v>42500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>52900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>51600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>49300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>46900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>44900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>48600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>38200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>49400</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3303,41 +3440,44 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>93700</v>
+      </c>
+      <c r="E60" s="3">
         <v>88900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>103200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>95600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>101300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>96400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>90800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>96800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>91800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>101600</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3359,41 +3499,44 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>576700</v>
+      </c>
+      <c r="E61" s="3">
         <v>603500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>629400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>636200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>643600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>635600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>636800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>636300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>637700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>570400</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -3415,41 +3558,44 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>91700</v>
+      </c>
+      <c r="E62" s="3">
         <v>88800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>82600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>90200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>88800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>106800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>148800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>176100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>159100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>144900</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3465,14 +3611,17 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3527,8 +3676,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3583,8 +3735,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3639,41 +3794,44 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>762200</v>
+      </c>
+      <c r="E66" s="3">
         <v>781200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>815300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>821900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>833700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>838800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>876400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>909200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>888600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>816900</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3695,8 +3853,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3717,8 +3878,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3773,8 +3935,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3829,8 +3994,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3885,8 +4053,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3941,41 +4112,44 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E72" s="3">
         <v>66800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>66000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>53000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>48800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>64000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>32400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-8100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-25000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-7000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3997,8 +4171,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4053,8 +4230,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4109,8 +4289,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4165,41 +4348,44 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>441200</v>
+      </c>
+      <c r="E76" s="3">
         <v>437900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>435400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>420400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>416000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>418300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>384400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>339400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>304500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>319800</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4221,8 +4407,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4277,58 +4466,61 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45200</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45109</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45018</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44836</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44745</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44654</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44465</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44374</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44283</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43918</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4338,53 +4530,56 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E81" s="3">
         <v>800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>13000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-15200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>31600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>40600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-18000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-30200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>23100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4900</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4394,8 +4589,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4416,55 +4614,56 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E83" s="3">
         <v>6500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4700</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -4472,8 +4671,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4528,8 +4730,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4584,8 +4789,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4640,8 +4848,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4696,8 +4907,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4752,53 +4966,56 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E89" s="3">
         <v>22500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>30700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>18300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-21500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>27400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>19000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>12800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>17600</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4808,8 +5025,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4830,55 +5050,56 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1700</v>
+        <v>-1500</v>
       </c>
       <c r="E91" s="3">
         <v>-1700</v>
       </c>
       <c r="F91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="G91" s="3">
         <v>-1000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -4886,8 +5107,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4942,8 +5166,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4998,55 +5225,58 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-62200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-57800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-158900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -5054,8 +5284,11 @@
       <c r="T94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5076,8 +5309,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5132,8 +5366,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5188,8 +5425,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5244,8 +5484,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5300,53 +5543,56 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-27400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>8300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-3300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>47900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>30800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>163000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>27500</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5356,35 +5602,38 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5397,8 +5646,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5412,53 +5661,56 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>21900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-13900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-13500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-31800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>15800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>16900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>43800</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5466,6 +5718,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
@@ -656,84 +656,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45200</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45109</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45018</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44836</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44745</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44654</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44465</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44374</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44283</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43918</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -743,115 +744,121 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>158600</v>
+      </c>
+      <c r="E8" s="3">
         <v>155700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>156500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>175300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>172200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>154200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>154800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>179400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>179800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>159700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>193000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>160300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>138400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>107200</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>106600</v>
+      </c>
+      <c r="E9" s="3">
         <v>95500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>98200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>105500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>104500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>106900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>106400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>104100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>117300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>105100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>94500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>111800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>94700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>83900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>63800</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -861,56 +868,59 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E10" s="3">
         <v>60200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>58300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>69800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>67700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>47300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>48400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>75300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>82800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>74700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>65200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>81200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>65600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>54500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>43400</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -920,8 +930,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -943,56 +956,57 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E12" s="3">
         <v>4900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6200</v>
-      </c>
-      <c r="G12" s="3">
-        <v>6700</v>
       </c>
       <c r="H12" s="3">
         <v>6700</v>
       </c>
       <c r="I12" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J12" s="3">
         <v>6000</v>
-      </c>
-      <c r="J12" s="3">
-        <v>8200</v>
       </c>
       <c r="K12" s="3">
         <v>8200</v>
       </c>
       <c r="L12" s="3">
+        <v>8200</v>
+      </c>
+      <c r="M12" s="3">
         <v>8100</v>
-      </c>
-      <c r="M12" s="3">
-        <v>7100</v>
       </c>
       <c r="N12" s="3">
         <v>7100</v>
       </c>
       <c r="O12" s="3">
+        <v>7100</v>
+      </c>
+      <c r="P12" s="3">
         <v>6000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>6300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5600</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1002,8 +1016,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1061,56 +1078,59 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>800</v>
+      </c>
+      <c r="E14" s="3">
         <v>-200</v>
-      </c>
-      <c r="E14" s="3">
-        <v>400</v>
       </c>
       <c r="F14" s="3">
         <v>400</v>
       </c>
       <c r="G14" s="3">
-        <v>1300</v>
+        <v>400</v>
       </c>
       <c r="H14" s="3">
         <v>1300</v>
       </c>
       <c r="I14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J14" s="3">
         <v>3700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>14000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>25000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>19700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2300</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1120,16 +1140,19 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E15" s="3">
         <v>3500</v>
-      </c>
-      <c r="E15" s="3">
-        <v>3700</v>
       </c>
       <c r="F15" s="3">
         <v>3700</v>
@@ -1150,37 +1173,40 @@
         <v>3700</v>
       </c>
       <c r="L15" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="M15" s="3">
         <v>3600</v>
       </c>
       <c r="N15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="O15" s="3">
         <v>3500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2700</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T15" s="3">
-        <v>0</v>
+      <c r="T15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1199,56 +1225,57 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>148600</v>
+      </c>
+      <c r="E17" s="3">
         <v>136200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>137200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>145300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>146200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>167700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>151700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>154300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>164000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>169300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>159200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>153000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>147600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>125400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>89500</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1258,56 +1285,59 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E18" s="3">
         <v>19500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>19300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>30000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>26000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-13500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>25100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>36100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>40000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>17700</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1317,8 +1347,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1340,44 +1373,45 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E20" s="3">
         <v>1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>7300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>37600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>27400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-17300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-24200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1387,8 +1421,8 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
@@ -1399,56 +1433,59 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E21" s="3">
         <v>26800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>23000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>33100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>30300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>47200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>58700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>37200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-17200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>45800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>18400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>17900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>22400</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1458,115 +1495,121 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E22" s="3">
         <v>18800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>18300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>13400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>10400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>10100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>11500</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E23" s="3">
         <v>1800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>17100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-19600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>30200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>43600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>24000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-33500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>28900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6200</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1576,67 +1619,73 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-4400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-3300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1300</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1694,56 +1743,59 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E26" s="3">
         <v>1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-15200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>31600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>40600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-18000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-30200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>23100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4900</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1753,56 +1805,59 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E27" s="3">
         <v>1200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>13000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-15200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>31600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>40600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-18000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-30200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>23100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4900</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1812,8 +1867,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1871,8 +1929,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1930,8 +1991,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1989,8 +2053,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2048,44 +2115,47 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-7300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-37600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-27400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>17300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>24200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2095,8 +2165,8 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
@@ -2107,56 +2177,59 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E33" s="3">
         <v>1200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>13000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-15200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>31600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>40600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-18000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-30200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>23100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4900</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2166,8 +2239,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2225,56 +2301,59 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E35" s="3">
         <v>1200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>13000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-15200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>31600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>40600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-18000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-30200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>23100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4900</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2284,61 +2363,64 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45200</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45109</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45018</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44836</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44745</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44654</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44465</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44374</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44283</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43918</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2348,8 +2430,11 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2371,8 +2456,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2394,8 +2480,9 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2403,35 +2490,35 @@
         <v>41100</v>
       </c>
       <c r="E41" s="3">
+        <v>41100</v>
+      </c>
+      <c r="F41" s="3">
         <v>36800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>42700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>26200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>30600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>44100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>36300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>53900</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2453,8 +2540,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2512,44 +2602,47 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E43" s="3">
         <v>48400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>47400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>57100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>56300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>47100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>59700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>58200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>63700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>51400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>55400</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2565,50 +2658,53 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>184000</v>
+      </c>
+      <c r="E44" s="3">
         <v>192300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>207200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>217500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>229000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>233600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>230500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>214900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>191100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>185000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>164300</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2624,50 +2720,53 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E45" s="3">
         <v>15700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>16000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>18000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>18200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>18500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>16900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>19000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8900</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2689,44 +2788,47 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>289800</v>
+      </c>
+      <c r="E46" s="3">
         <v>297400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>304700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>333300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>324200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>325000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>325300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>320500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>314300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>291700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>282600</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2748,8 +2850,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2798,8 +2903,8 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="S47" s="3">
+        <v>0</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -2807,44 +2912,47 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>74900</v>
+      </c>
+      <c r="E48" s="3">
         <v>76500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>78400</v>
-      </c>
-      <c r="F48" s="3">
-        <v>78700</v>
       </c>
       <c r="G48" s="3">
         <v>78700</v>
       </c>
       <c r="H48" s="3">
+        <v>78700</v>
+      </c>
+      <c r="I48" s="3">
         <v>81700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>86000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>88800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>88000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>51500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>50400</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,50 +2968,53 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T48" s="3">
-        <v>0</v>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>826000</v>
+      </c>
+      <c r="E49" s="3">
         <v>829500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>832800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>836700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>839400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>843000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>845700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>851500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>846400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>849800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>803700</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2919,14 +3030,17 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2984,8 +3098,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3043,23 +3160,26 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3">
         <v>3200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>2100</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3075,8 +3195,8 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -3102,8 +3222,11 @@
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3161,44 +3284,47 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1191700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1203300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1219100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1250700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1242300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1249600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1257100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1260800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1248700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1193100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1136700</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3220,8 +3346,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3243,8 +3372,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3266,44 +3396,45 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>50300</v>
+      </c>
+      <c r="E57" s="3">
         <v>43700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>39800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>43800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>37400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>44900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>43500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>39600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>41900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>45700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>46600</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3319,22 +3450,25 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E58" s="3">
         <v>7500</v>
-      </c>
-      <c r="E58" s="3">
-        <v>6600</v>
       </c>
       <c r="F58" s="3">
         <v>6600</v>
@@ -3343,26 +3477,26 @@
         <v>6600</v>
       </c>
       <c r="H58" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I58" s="3">
         <v>7000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>6300</v>
       </c>
       <c r="K58" s="3">
         <v>6300</v>
       </c>
       <c r="L58" s="3">
+        <v>6300</v>
+      </c>
+      <c r="M58" s="3">
         <v>7900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5500</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3384,44 +3518,47 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E59" s="3">
         <v>42600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>52900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>51600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>49300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>46900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>44900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>48600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>38200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>49400</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3443,44 +3580,47 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>101700</v>
+      </c>
+      <c r="E60" s="3">
         <v>93700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>88900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>103200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>95600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>101300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>96400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>90800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>96800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>91800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>101600</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3502,44 +3642,47 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>560100</v>
+      </c>
+      <c r="E61" s="3">
         <v>576700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>603500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>629400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>636200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>643600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>635600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>636800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>636300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>637700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>570400</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3561,44 +3704,47 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>85000</v>
+      </c>
+      <c r="E62" s="3">
         <v>91700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>88800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>82600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>90200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>88800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>106800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>148800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>176100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>159100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>144900</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3614,14 +3760,17 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3679,8 +3828,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3738,8 +3890,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3797,44 +3952,47 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>746800</v>
+      </c>
+      <c r="E66" s="3">
         <v>762200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>781200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>815300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>821900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>833700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>838800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>876400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>909200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>888600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>816900</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3856,8 +4014,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3879,8 +4040,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3938,8 +4100,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3997,8 +4162,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4056,8 +4224,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4115,44 +4286,47 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>71700</v>
+      </c>
+      <c r="E72" s="3">
         <v>68000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>66800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>66000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>53000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>48800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>64000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>32400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-8100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-25000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-7000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4174,8 +4348,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4233,8 +4410,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4292,8 +4472,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4351,44 +4534,47 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>444900</v>
+      </c>
+      <c r="E76" s="3">
         <v>441200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>437900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>435400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>420400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>416000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>418300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>384400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>339400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>304500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>319800</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4410,8 +4596,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4469,61 +4658,64 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45200</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45109</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45018</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44836</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44745</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44654</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44465</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44374</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44283</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43918</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4533,56 +4725,59 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E81" s="3">
         <v>1200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>13000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-15200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>31600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>40600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-18000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-30200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>23100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4900</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4592,8 +4787,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4615,58 +4813,59 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E83" s="3">
         <v>6100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4700</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -4674,8 +4873,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4733,8 +4935,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4792,8 +4997,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4851,8 +5059,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4910,8 +5121,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4969,56 +5183,59 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E89" s="3">
         <v>31200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>22500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>30700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>18300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-3300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-21500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>27400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>19000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>17600</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5028,8 +5245,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5051,58 +5271,59 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-1700</v>
       </c>
       <c r="F91" s="3">
         <v>-1700</v>
       </c>
       <c r="G91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="H91" s="3">
         <v>-1000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T91" s="3">
         <v>0</v>
@@ -5110,8 +5331,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5169,8 +5393,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5228,58 +5455,61 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-16200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-62200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-57800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-158900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1300</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -5287,8 +5517,11 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5310,8 +5543,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5369,8 +5603,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5428,8 +5665,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5487,8 +5727,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5546,56 +5789,59 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-17700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-26000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-27400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>8300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>47900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>30800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>163000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>27500</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5605,38 +5851,41 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5649,8 +5898,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -5664,56 +5913,59 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>4200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>21900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-13900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-17600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-31800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>16900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>43800</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5721,6 +5973,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
@@ -656,88 +656,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45200</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45109</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45018</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44836</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44745</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44654</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44374</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44283</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43918</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -747,121 +748,127 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>169500</v>
+      </c>
+      <c r="E8" s="3">
         <v>158600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>155700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>156500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>175300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>172200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>154200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>154800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>179400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>200100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>179800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>159700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>193000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>160300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>138400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>107200</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U8" s="3">
-        <v>0</v>
+      <c r="U8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>99200</v>
+      </c>
+      <c r="E9" s="3">
         <v>106600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>95500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>98200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>105500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>104500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>106900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>106400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>104100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>117300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>105100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>94500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>111800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>94700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>83900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>63800</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -871,59 +878,62 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>70300</v>
+      </c>
+      <c r="E10" s="3">
         <v>52000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>60200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>58300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>69800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>67700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>47300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>48400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>75300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>82800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>74700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>65200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>81200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>65600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>54500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>43400</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -933,8 +943,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -957,59 +970,60 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E12" s="3">
         <v>4800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6200</v>
-      </c>
-      <c r="H12" s="3">
-        <v>6700</v>
       </c>
       <c r="I12" s="3">
         <v>6700</v>
       </c>
       <c r="J12" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K12" s="3">
         <v>6000</v>
-      </c>
-      <c r="K12" s="3">
-        <v>8200</v>
       </c>
       <c r="L12" s="3">
         <v>8200</v>
       </c>
       <c r="M12" s="3">
+        <v>8200</v>
+      </c>
+      <c r="N12" s="3">
         <v>8100</v>
-      </c>
-      <c r="N12" s="3">
-        <v>7100</v>
       </c>
       <c r="O12" s="3">
         <v>7100</v>
       </c>
       <c r="P12" s="3">
+        <v>7100</v>
+      </c>
+      <c r="Q12" s="3">
         <v>6000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>6300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5600</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1019,8 +1033,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1081,59 +1098,62 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-200</v>
-      </c>
-      <c r="F14" s="3">
-        <v>400</v>
       </c>
       <c r="G14" s="3">
         <v>400</v>
       </c>
       <c r="H14" s="3">
-        <v>1300</v>
+        <v>400</v>
       </c>
       <c r="I14" s="3">
         <v>1300</v>
       </c>
       <c r="J14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K14" s="3">
         <v>3700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>14000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>25000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>19700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2300</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1143,8 +1163,11 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1152,10 +1175,10 @@
         <v>3400</v>
       </c>
       <c r="E15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F15" s="3">
         <v>3500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>3700</v>
       </c>
       <c r="G15" s="3">
         <v>3700</v>
@@ -1176,37 +1199,40 @@
         <v>3700</v>
       </c>
       <c r="M15" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="N15" s="3">
         <v>3600</v>
       </c>
       <c r="O15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="P15" s="3">
         <v>3500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2700</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1226,59 +1252,60 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>141600</v>
+      </c>
+      <c r="E17" s="3">
         <v>148600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>136200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>137200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>145300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>146200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>167700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>151700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>154300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>164000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>169300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>159200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>153000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>147600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>125400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>89500</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1288,59 +1315,62 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E18" s="3">
         <v>10000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>19500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>19300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>30000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>26000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>25100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>36100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>10500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>40000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>17700</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1350,8 +1380,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1374,47 +1407,48 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E20" s="3">
         <v>3800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>7300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>37600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>27400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-17300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-24200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1424,8 +1458,8 @@
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
@@ -1436,59 +1470,62 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E21" s="3">
         <v>19700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>26800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>23000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>33100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>30300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>47200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>58700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>37200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-17200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>45800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>18400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>17900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>22400</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1498,121 +1535,127 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E22" s="3">
         <v>11000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>18800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>18300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>13400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>10400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>10100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>11900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11500</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E23" s="3">
         <v>2800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>17100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-19600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>30200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>43600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>24000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-33500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>28900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6200</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1622,70 +1665,76 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-4400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1300</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1746,59 +1795,62 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E26" s="3">
         <v>3700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>13000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-15200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>31600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>40600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-18000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-30200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>23100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4900</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,59 +1860,62 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E27" s="3">
         <v>3700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>13000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-15200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>31600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>40600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-18000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-30200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>23100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4900</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1870,8 +1925,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1932,8 +1990,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1994,8 +2055,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2056,8 +2120,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2118,47 +2185,50 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-7300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-37600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-27400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>17300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>24200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2168,8 +2238,8 @@
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
@@ -2180,59 +2250,62 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E33" s="3">
         <v>3700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>13000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-15200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>31600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>40600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-18000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-30200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>23100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4900</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2242,8 +2315,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2304,59 +2380,62 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E35" s="3">
         <v>3700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>13000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-15200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>31600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>40600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-18000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-30200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>23100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4900</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,64 +2445,67 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45200</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45109</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45018</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44836</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44745</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44654</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44374</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44283</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43918</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2433,8 +2515,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2457,8 +2542,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2481,47 +2567,48 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>41100</v>
+        <v>53100</v>
       </c>
       <c r="E41" s="3">
         <v>41100</v>
       </c>
       <c r="F41" s="3">
+        <v>41100</v>
+      </c>
+      <c r="G41" s="3">
         <v>36800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>42700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>26200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>30600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>44100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>36300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>53900</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2543,8 +2630,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2605,47 +2695,50 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E43" s="3">
         <v>48700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>48400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>47400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>57100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>56300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>47100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>59700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>58200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>63700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>51400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>55400</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2661,53 +2754,56 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
+      <c r="U43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>173500</v>
+      </c>
+      <c r="E44" s="3">
         <v>184000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>192300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>207200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>217500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>229000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>233600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>230500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>214900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>191100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>185000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>164300</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2723,53 +2819,56 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E45" s="3">
         <v>15900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>15700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>16000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>18000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>18200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>18500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>19000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8900</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,47 +2890,50 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>301100</v>
+      </c>
+      <c r="E46" s="3">
         <v>289800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>297400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>304700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>333300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>324200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>325000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>325300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>320500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>314300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>291700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>282600</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2853,8 +2955,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2906,8 +3011,8 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
+      <c r="T47" s="3">
+        <v>0</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
@@ -2915,47 +3020,50 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>73300</v>
+      </c>
+      <c r="E48" s="3">
         <v>74900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>76500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>78400</v>
-      </c>
-      <c r="G48" s="3">
-        <v>78700</v>
       </c>
       <c r="H48" s="3">
         <v>78700</v>
       </c>
       <c r="I48" s="3">
+        <v>78700</v>
+      </c>
+      <c r="J48" s="3">
         <v>81700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>86000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>88800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>88000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>51500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>50400</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2971,53 +3079,56 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U48" s="3">
-        <v>0</v>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>822500</v>
+      </c>
+      <c r="E49" s="3">
         <v>826000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>829500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>832800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>836700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>839400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>843000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>845700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>851500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>846400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>849800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>803700</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3033,14 +3144,17 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3101,8 +3215,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3163,26 +3280,29 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E52" s="3">
         <v>1100</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3">
         <v>3200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3198,8 +3318,8 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
+      <c r="N52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O52" s="3">
         <v>0</v>
@@ -3225,8 +3345,11 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3287,47 +3410,50 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1198100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1191700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1203300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1219100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1250700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1242300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1249600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1257100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1260800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1248700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1193100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1136700</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3475,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3373,8 +3502,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3397,47 +3527,48 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E57" s="3">
         <v>50300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>43700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>39800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>43800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>37400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>44900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>43500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>39600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>41900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>45700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>46600</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3453,14 +3584,17 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3468,10 +3602,10 @@
         <v>7400</v>
       </c>
       <c r="E58" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F58" s="3">
         <v>7500</v>
-      </c>
-      <c r="F58" s="3">
-        <v>6600</v>
       </c>
       <c r="G58" s="3">
         <v>6600</v>
@@ -3480,26 +3614,26 @@
         <v>6600</v>
       </c>
       <c r="I58" s="3">
+        <v>6600</v>
+      </c>
+      <c r="J58" s="3">
         <v>7000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6000</v>
-      </c>
-      <c r="K58" s="3">
-        <v>6300</v>
       </c>
       <c r="L58" s="3">
         <v>6300</v>
       </c>
       <c r="M58" s="3">
+        <v>6300</v>
+      </c>
+      <c r="N58" s="3">
         <v>7900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5500</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3521,47 +3655,50 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>41500</v>
+      </c>
+      <c r="E59" s="3">
         <v>44000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>42600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>42500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>52900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>51600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>49300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>46900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>44900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>48600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>38200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>49400</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3583,47 +3720,50 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>107500</v>
+      </c>
+      <c r="E60" s="3">
         <v>101700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>93700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>88900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>103200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>95600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>101300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>96400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>90800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>96800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>91800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>101600</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,47 +3785,50 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>548700</v>
+      </c>
+      <c r="E61" s="3">
         <v>560100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>576700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>603500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>629400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>636200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>643600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>635600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>636800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>636300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>637700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>570400</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3707,47 +3850,50 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E62" s="3">
         <v>85000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>91700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>88800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>82600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>90200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>88800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>106800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>148800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>176100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>159100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>144900</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3763,14 +3909,17 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3831,8 +3980,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3893,8 +4045,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3955,47 +4110,50 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>734900</v>
+      </c>
+      <c r="E66" s="3">
         <v>746800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>762200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>781200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>815300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>821900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>833700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>838800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>876400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>909200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>888600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>816900</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4017,8 +4175,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4041,8 +4202,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4103,8 +4265,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4165,8 +4330,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4227,8 +4395,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4289,47 +4460,50 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>88800</v>
+      </c>
+      <c r="E72" s="3">
         <v>71700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>68000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>66800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>66000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>53000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>48800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>64000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>32400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-8100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-25000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-7000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4351,8 +4525,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4413,8 +4590,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4475,8 +4655,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4537,47 +4720,50 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>463200</v>
+      </c>
+      <c r="E76" s="3">
         <v>444900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>441200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>437900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>435400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>420400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>416000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>418300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>384400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>339400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>304500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>319800</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4599,8 +4785,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4661,64 +4850,67 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45200</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45109</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45018</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44836</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44745</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44654</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44374</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44283</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43918</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4728,59 +4920,62 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E81" s="3">
         <v>3700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>13000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-15200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>31600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>40600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-18000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-30200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>23100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4900</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +4985,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4814,61 +5012,62 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E83" s="3">
         <v>5900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4700</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T83" s="3">
-        <v>0</v>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U83" s="3">
         <v>0</v>
@@ -4876,8 +5075,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4938,8 +5140,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5000,8 +5205,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5062,8 +5270,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5124,8 +5335,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5186,59 +5400,62 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E89" s="3">
         <v>18800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>31200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>22500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>18300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-21500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>27400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>19000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>12800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>17600</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5248,8 +5465,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5272,61 +5492,62 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-1700</v>
       </c>
       <c r="G91" s="3">
         <v>-1700</v>
       </c>
       <c r="H91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="I91" s="3">
         <v>-1000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1300</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
@@ -5334,8 +5555,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5396,8 +5620,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5458,61 +5685,64 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-62200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-57800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-158900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1300</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -5520,8 +5750,11 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5544,8 +5777,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5606,8 +5840,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5668,8 +5905,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5730,8 +5970,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5792,59 +6035,62 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-12400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-17700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-26000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-27400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-8400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>8300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>47900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>30800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>163000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>27500</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5854,8 +6100,11 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5863,32 +6112,32 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5901,8 +6150,8 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -5916,59 +6165,62 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>4200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>21900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-13900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-31800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>16900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>43800</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5976,6 +6228,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
   <si>
     <t>HLLY</t>
   </si>
@@ -656,92 +656,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45200</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45109</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45018</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44836</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44745</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44654</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44465</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44374</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44283</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -751,127 +752,133 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>134000</v>
+      </c>
+      <c r="E8" s="3">
         <v>169500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>158600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>155700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>156500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>175300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>172200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>154200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>154800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>179400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>200100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>179800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>159700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>193000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>160300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>138400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>107200</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>81700</v>
+      </c>
+      <c r="E9" s="3">
         <v>99200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>106600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>95500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>98200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>105500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>104500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>106900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>106400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>104100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>117300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>105100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>94500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>111800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>94700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>83900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>63800</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -881,62 +888,65 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>52300</v>
+      </c>
+      <c r="E10" s="3">
         <v>70300</v>
       </c>
-      <c r="E10" s="3">
-        <v>52000</v>
-      </c>
       <c r="F10" s="3">
-        <v>60200</v>
+        <v>52100</v>
       </c>
       <c r="G10" s="3">
-        <v>58300</v>
+        <v>60300</v>
       </c>
       <c r="H10" s="3">
-        <v>69800</v>
+        <v>58400</v>
       </c>
       <c r="I10" s="3">
+        <v>69700</v>
+      </c>
+      <c r="J10" s="3">
         <v>67700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>47300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>48400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>75300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>82800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>74700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>65200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>81200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>65600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>54500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>43400</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -946,8 +956,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -971,62 +984,63 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E12" s="3">
         <v>4300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6200</v>
-      </c>
-      <c r="I12" s="3">
-        <v>6700</v>
       </c>
       <c r="J12" s="3">
         <v>6700</v>
       </c>
       <c r="K12" s="3">
+        <v>6700</v>
+      </c>
+      <c r="L12" s="3">
         <v>6000</v>
-      </c>
-      <c r="L12" s="3">
-        <v>8200</v>
       </c>
       <c r="M12" s="3">
         <v>8200</v>
       </c>
       <c r="N12" s="3">
+        <v>8200</v>
+      </c>
+      <c r="O12" s="3">
         <v>8100</v>
-      </c>
-      <c r="O12" s="3">
-        <v>7100</v>
       </c>
       <c r="P12" s="3">
         <v>7100</v>
       </c>
       <c r="Q12" s="3">
+        <v>7100</v>
+      </c>
+      <c r="R12" s="3">
         <v>6000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>6300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5600</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1036,8 +1050,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1101,62 +1118,65 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="E14" s="3">
-        <v>800</v>
+        <v>-1100</v>
       </c>
       <c r="F14" s="3">
-        <v>-200</v>
+        <v>100</v>
       </c>
       <c r="G14" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H14" s="3">
-        <v>400</v>
+        <v>1100</v>
       </c>
       <c r="I14" s="3">
         <v>1300</v>
       </c>
       <c r="J14" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K14" s="3">
         <v>1300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>14000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>25000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>19700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2300</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1166,8 +1186,11 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1178,10 +1201,10 @@
         <v>3400</v>
       </c>
       <c r="F15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G15" s="3">
         <v>3500</v>
-      </c>
-      <c r="G15" s="3">
-        <v>3700</v>
       </c>
       <c r="H15" s="3">
         <v>3700</v>
@@ -1202,37 +1225,40 @@
         <v>3700</v>
       </c>
       <c r="N15" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="O15" s="3">
         <v>3600</v>
       </c>
       <c r="P15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="Q15" s="3">
         <v>3500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2700</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1253,62 +1279,63 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E17" s="3">
         <v>141600</v>
       </c>
-      <c r="E17" s="3">
-        <v>148600</v>
-      </c>
       <c r="F17" s="3">
-        <v>136200</v>
+        <v>147800</v>
       </c>
       <c r="G17" s="3">
-        <v>137200</v>
+        <v>136100</v>
       </c>
       <c r="H17" s="3">
-        <v>145300</v>
+        <v>136800</v>
       </c>
       <c r="I17" s="3">
-        <v>146200</v>
+        <v>145000</v>
       </c>
       <c r="J17" s="3">
+        <v>144900</v>
+      </c>
+      <c r="K17" s="3">
         <v>167700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>151700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>154300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>164000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>169300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>159200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>153000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>147600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>125400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>89500</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1318,62 +1345,65 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E18" s="3">
         <v>27900</v>
       </c>
-      <c r="E18" s="3">
-        <v>10000</v>
-      </c>
       <c r="F18" s="3">
-        <v>19500</v>
+        <v>10800</v>
       </c>
       <c r="G18" s="3">
-        <v>19300</v>
+        <v>19600</v>
       </c>
       <c r="H18" s="3">
-        <v>30000</v>
+        <v>19700</v>
       </c>
       <c r="I18" s="3">
-        <v>26000</v>
+        <v>30300</v>
       </c>
       <c r="J18" s="3">
+        <v>27300</v>
+      </c>
+      <c r="K18" s="3">
         <v>-13500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>25100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>36100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>40000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>17700</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1383,8 +1413,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1408,50 +1441,51 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>4500</v>
+        <v>-1000</v>
       </c>
       <c r="E20" s="3">
-        <v>3800</v>
+        <v>-3400</v>
       </c>
       <c r="F20" s="3">
-        <v>1200</v>
+        <v>-3100</v>
       </c>
       <c r="G20" s="3">
-        <v>-2700</v>
+        <v>-1100</v>
       </c>
       <c r="H20" s="3">
-        <v>-3000</v>
+        <v>2100</v>
       </c>
       <c r="I20" s="3">
-        <v>-1900</v>
+        <v>2000</v>
       </c>
       <c r="J20" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K20" s="3">
         <v>7300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>37600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>27400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-17300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-24200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1461,8 +1495,8 @@
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
@@ -1473,62 +1507,65 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>38400</v>
+        <v>18500</v>
       </c>
       <c r="E21" s="3">
-        <v>19700</v>
+        <v>34700</v>
       </c>
       <c r="F21" s="3">
-        <v>26800</v>
+        <v>17400</v>
       </c>
       <c r="G21" s="3">
-        <v>23000</v>
+        <v>24300</v>
       </c>
       <c r="H21" s="3">
-        <v>33100</v>
+        <v>21400</v>
       </c>
       <c r="I21" s="3">
-        <v>30300</v>
+        <v>32000</v>
       </c>
       <c r="J21" s="3">
+        <v>29600</v>
+      </c>
+      <c r="K21" s="3">
         <v>200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>47200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>58700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>37200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-17200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>45800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>18400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>17900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>22400</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1538,127 +1575,133 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E22" s="3">
         <v>13200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>11000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>18800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>13700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>10400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>9900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>10100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11500</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E23" s="3">
         <v>19200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>17100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-19600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>30200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>43600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>24000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-14800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-33500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>28900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6200</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1668,73 +1711,79 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E24" s="3">
         <v>2100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-4400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1300</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1798,62 +1847,65 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E26" s="3">
         <v>17100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>13000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-15200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>31600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>40600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-30200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>23100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4900</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1863,62 +1915,65 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E27" s="3">
         <v>17100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>13000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-15200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>31600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>40600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-30200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>23100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4900</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1928,8 +1983,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1993,8 +2051,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2058,8 +2119,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2123,8 +2187,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2188,50 +2255,53 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-4500</v>
+        <v>1000</v>
       </c>
       <c r="E32" s="3">
-        <v>-3800</v>
+        <v>3400</v>
       </c>
       <c r="F32" s="3">
-        <v>-1200</v>
+        <v>3100</v>
       </c>
       <c r="G32" s="3">
-        <v>2700</v>
+        <v>1100</v>
       </c>
       <c r="H32" s="3">
-        <v>3000</v>
+        <v>-2100</v>
       </c>
       <c r="I32" s="3">
-        <v>1900</v>
+        <v>-2000</v>
       </c>
       <c r="J32" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-7300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-37600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-27400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>17300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>24200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2241,8 +2311,8 @@
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
@@ -2253,62 +2323,65 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E33" s="3">
         <v>17100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-15200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>31600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>40600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-30200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>23100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4900</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2318,8 +2391,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2383,62 +2459,65 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E35" s="3">
         <v>17100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-15200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>31600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>40600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-30200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>23100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4900</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2448,67 +2527,70 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45200</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45109</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45018</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44836</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44745</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44654</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44465</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44374</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44283</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2518,8 +2600,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2543,8 +2628,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2568,50 +2654,51 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E41" s="3">
         <v>53100</v>
-      </c>
-      <c r="E41" s="3">
-        <v>41100</v>
       </c>
       <c r="F41" s="3">
         <v>41100</v>
       </c>
       <c r="G41" s="3">
+        <v>41100</v>
+      </c>
+      <c r="H41" s="3">
         <v>36800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>42700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>44100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>36300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>53900</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2633,8 +2720,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2698,50 +2788,53 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E43" s="3">
         <v>56100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>48700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>48400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>47400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>57100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>56300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>47100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>59700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>58200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>63700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>51400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>55400</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2757,56 +2850,59 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>179300</v>
+      </c>
+      <c r="E44" s="3">
         <v>173500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>184000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>192300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>207200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>217500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>229000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>233600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>230500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>214900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>191100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>185000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>164300</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2822,56 +2918,59 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>18400</v>
+        <v>7700</v>
       </c>
       <c r="E45" s="3">
-        <v>15900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>15700</v>
-      </c>
-      <c r="G45" s="3">
-        <v>13300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>16000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>18000</v>
-      </c>
-      <c r="J45" s="3">
+        <v>2100</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>18200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>18500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>19000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8900</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2893,50 +2992,53 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>298600</v>
+      </c>
+      <c r="E46" s="3">
         <v>301100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>289800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>297400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>304700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>333300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>324200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>325000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>325300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>320500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>314300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>291700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>282600</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2958,31 +3060,34 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
+        <v>1100</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+        <v>2100</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3014,8 +3119,8 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="U47" s="3">
+        <v>0</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
@@ -3023,50 +3128,53 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E48" s="3">
         <v>73300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>74900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>76500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>78400</v>
-      </c>
-      <c r="H48" s="3">
-        <v>78700</v>
       </c>
       <c r="I48" s="3">
         <v>78700</v>
       </c>
       <c r="J48" s="3">
+        <v>78700</v>
+      </c>
+      <c r="K48" s="3">
         <v>81700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>86000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>88800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>88000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>51500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>50400</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3082,56 +3190,59 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>812000</v>
+      </c>
+      <c r="E49" s="3">
         <v>822500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>826000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>829500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>832800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>836700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>839400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>843000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>845700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>851500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>846400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>849800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>803700</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3147,14 +3258,17 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3218,8 +3332,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3283,25 +3400,28 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>1200</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1100</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G52" s="3">
-        <v>3200</v>
-      </c>
-      <c r="H52" s="3">
-        <v>2100</v>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
@@ -3321,8 +3441,8 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P52" s="3">
         <v>0</v>
@@ -3348,8 +3468,11 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3413,50 +3536,53 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1184200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1198100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1191700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1203300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1219100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1250700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1242300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1249600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1257100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1260800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1248700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1193100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1136700</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3478,8 +3604,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3503,8 +3632,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3528,50 +3658,51 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>52700</v>
+      </c>
+      <c r="E57" s="3">
         <v>58600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>50300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>43700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>39800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>43800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>37400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>44900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>43500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>39600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>41900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>45700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>46600</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3587,56 +3718,59 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7400</v>
+        <v>11800</v>
       </c>
       <c r="E58" s="3">
-        <v>7400</v>
+        <v>11700</v>
       </c>
       <c r="F58" s="3">
-        <v>7500</v>
+        <v>11900</v>
       </c>
       <c r="G58" s="3">
-        <v>6600</v>
+        <v>12400</v>
       </c>
       <c r="H58" s="3">
-        <v>6600</v>
+        <v>11800</v>
       </c>
       <c r="I58" s="3">
-        <v>6600</v>
+        <v>11700</v>
       </c>
       <c r="J58" s="3">
+        <v>11500</v>
+      </c>
+      <c r="K58" s="3">
         <v>7000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6000</v>
-      </c>
-      <c r="L58" s="3">
-        <v>6300</v>
       </c>
       <c r="M58" s="3">
         <v>6300</v>
       </c>
       <c r="N58" s="3">
+        <v>6300</v>
+      </c>
+      <c r="O58" s="3">
         <v>7900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5500</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3658,50 +3792,53 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>41500</v>
+        <v>12800</v>
       </c>
       <c r="E59" s="3">
-        <v>44000</v>
+        <v>14000</v>
       </c>
       <c r="F59" s="3">
-        <v>42600</v>
+        <v>18400</v>
       </c>
       <c r="G59" s="3">
-        <v>42500</v>
+        <v>16100</v>
       </c>
       <c r="H59" s="3">
-        <v>52900</v>
+        <v>9800</v>
       </c>
       <c r="I59" s="3">
-        <v>51600</v>
+        <v>14900</v>
       </c>
       <c r="J59" s="3">
+        <v>15000</v>
+      </c>
+      <c r="K59" s="3">
         <v>49300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>46900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>44900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>48600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>38200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>49400</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3723,50 +3860,53 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>101900</v>
+      </c>
+      <c r="E60" s="3">
         <v>107500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>101700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>93700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>88900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>103200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>95600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>101300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>96400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>90800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>96800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>91800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>101600</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3788,50 +3928,53 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>548700</v>
+        <v>576700</v>
       </c>
       <c r="E61" s="3">
-        <v>560100</v>
+        <v>575100</v>
       </c>
       <c r="F61" s="3">
-        <v>576700</v>
+        <v>585400</v>
       </c>
       <c r="G61" s="3">
-        <v>603500</v>
+        <v>603100</v>
       </c>
       <c r="H61" s="3">
-        <v>629400</v>
+        <v>629500</v>
       </c>
       <c r="I61" s="3">
-        <v>636200</v>
+        <v>654000</v>
       </c>
       <c r="J61" s="3">
+        <v>662900</v>
+      </c>
+      <c r="K61" s="3">
         <v>643600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>635600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>636800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>636300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>637700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>570400</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3853,50 +3996,53 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>78700</v>
+        <v>2000</v>
       </c>
       <c r="E62" s="3">
-        <v>85000</v>
+        <v>3600</v>
       </c>
       <c r="F62" s="3">
-        <v>91700</v>
+        <v>8100</v>
       </c>
       <c r="G62" s="3">
+        <v>11900</v>
+      </c>
+      <c r="H62" s="3">
+        <v>13100</v>
+      </c>
+      <c r="I62" s="3">
+        <v>10300</v>
+      </c>
+      <c r="J62" s="3">
+        <v>7300</v>
+      </c>
+      <c r="K62" s="3">
         <v>88800</v>
       </c>
-      <c r="H62" s="3">
-        <v>82600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>90200</v>
-      </c>
-      <c r="J62" s="3">
-        <v>88800</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>106800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>148800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>176100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>159100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>144900</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3912,14 +4058,17 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3983,8 +4132,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4048,8 +4200,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4113,50 +4268,53 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>725500</v>
+      </c>
+      <c r="E66" s="3">
         <v>734900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>746800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>762200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>781200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>815300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>821900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>833700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>838800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>876400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>909200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>888600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>816900</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4178,8 +4336,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4203,8 +4364,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4268,8 +4430,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4333,8 +4498,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4398,8 +4566,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4463,50 +4634,53 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E72" s="3">
         <v>88800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>71700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>68000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>66800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>66000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>53000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>48800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>64000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>32400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-8100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-25000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-7000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4528,8 +4702,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4593,8 +4770,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4658,8 +4838,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4723,50 +4906,53 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>458700</v>
+      </c>
+      <c r="E76" s="3">
         <v>463200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>444900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>441200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>437900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>435400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>420400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>416000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>418300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>384400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>339400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>304500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>319800</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4788,8 +4974,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4853,67 +5042,70 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45200</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45109</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45018</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44836</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44745</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44654</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44465</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44374</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44283</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4923,62 +5115,65 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E81" s="3">
         <v>17100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-15200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>31600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>40600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-30200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>23100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4900</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4988,8 +5183,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5013,64 +5211,65 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>6100</v>
+        <v>4100</v>
       </c>
       <c r="E83" s="3">
-        <v>5900</v>
+        <v>3800</v>
       </c>
       <c r="F83" s="3">
-        <v>6100</v>
+        <v>3900</v>
       </c>
       <c r="G83" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I83" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J83" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="L83" s="3">
         <v>6500</v>
       </c>
-      <c r="H83" s="3">
-        <v>6100</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="M83" s="3">
         <v>6200</v>
       </c>
-      <c r="J83" s="3">
-        <v>6300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>6500</v>
-      </c>
-      <c r="L83" s="3">
-        <v>6200</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4700</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -5078,8 +5277,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5143,8 +5345,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5208,8 +5413,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5273,8 +5481,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5338,8 +5549,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5403,62 +5617,65 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E89" s="3">
         <v>25700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>18800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>31200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>22500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>30700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>18300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-3300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-21500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>27400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>19000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>12800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>17600</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,8 +5685,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5493,64 +5713,65 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-1700</v>
       </c>
       <c r="H91" s="3">
         <v>-1700</v>
       </c>
       <c r="I91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J91" s="3">
         <v>-1000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -5558,8 +5779,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5623,8 +5847,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5688,64 +5915,67 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-62200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-57800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-158900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1300</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -5753,8 +5983,11 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5778,31 +6011,32 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5843,8 +6077,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5908,8 +6145,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5973,8 +6213,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6038,62 +6281,65 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-12400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-17700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-26000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-27400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>8300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-3300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>47900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>30800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>163000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>27500</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6103,44 +6349,47 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G101" s="3">
-        <v>-200</v>
+        <v>800</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="I101" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="J101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K101" s="3">
         <v>800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6153,8 +6402,8 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -6168,62 +6417,65 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E102" s="3">
         <v>12000</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>4200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>21900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>9500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-13900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-17600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-31800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>16900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>43800</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6231,6 +6483,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
   <si>
     <t>HLLY</t>
   </si>
@@ -656,96 +656,96 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45564</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45200</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45109</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45018</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44836</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44745</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44654</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44374</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44283</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43918</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -755,133 +755,139 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>140100</v>
+      </c>
+      <c r="E8" s="3">
         <v>134000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>169500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>158600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>155700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>156500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>175300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>172200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>154200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>154800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>179400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>200100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>179800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>159700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>193000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>160300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>138400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>107200</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E9" s="3">
         <v>81700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>99200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>106600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>95500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>98200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>105500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>104500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>106900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>106400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>104100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>117300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>105100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>94500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>111800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>94700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>83900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>63800</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -891,65 +897,68 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>72100</v>
+      </c>
+      <c r="E10" s="3">
         <v>52300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>70300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>52100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>60300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>58400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>69700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>67700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>47300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>48400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>75300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>82800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>74700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>65200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>81200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>65600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>54500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>43400</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -959,8 +968,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -985,65 +997,66 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E12" s="3">
         <v>4600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>6100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6200</v>
-      </c>
-      <c r="J12" s="3">
-        <v>6700</v>
       </c>
       <c r="K12" s="3">
         <v>6700</v>
       </c>
       <c r="L12" s="3">
+        <v>6700</v>
+      </c>
+      <c r="M12" s="3">
         <v>6000</v>
-      </c>
-      <c r="M12" s="3">
-        <v>8200</v>
       </c>
       <c r="N12" s="3">
         <v>8200</v>
       </c>
       <c r="O12" s="3">
+        <v>8200</v>
+      </c>
+      <c r="P12" s="3">
         <v>8100</v>
-      </c>
-      <c r="P12" s="3">
-        <v>7100</v>
       </c>
       <c r="Q12" s="3">
         <v>7100</v>
       </c>
       <c r="R12" s="3">
+        <v>7100</v>
+      </c>
+      <c r="S12" s="3">
         <v>6000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5600</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1053,8 +1066,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1121,65 +1137,68 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E14" s="3">
         <v>7800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1100</v>
-      </c>
-      <c r="F14" s="3">
-        <v>100</v>
       </c>
       <c r="G14" s="3">
         <v>100</v>
       </c>
       <c r="H14" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I14" s="3">
         <v>1100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>14000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>25000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>19700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>7500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2300</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1189,13 +1208,16 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>3400</v>
+        <v>3600</v>
       </c>
       <c r="E15" s="3">
         <v>3400</v>
@@ -1204,10 +1226,10 @@
         <v>3400</v>
       </c>
       <c r="G15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="H15" s="3">
         <v>3500</v>
-      </c>
-      <c r="H15" s="3">
-        <v>3700</v>
       </c>
       <c r="I15" s="3">
         <v>3700</v>
@@ -1228,37 +1250,40 @@
         <v>3700</v>
       </c>
       <c r="O15" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="P15" s="3">
         <v>3600</v>
       </c>
       <c r="Q15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="R15" s="3">
         <v>3500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2700</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1280,65 +1305,66 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>109900</v>
+      </c>
+      <c r="E17" s="3">
         <v>120000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>141600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>147800</v>
       </c>
-      <c r="G17" s="3">
-        <v>136100</v>
-      </c>
       <c r="H17" s="3">
+        <v>136200</v>
+      </c>
+      <c r="I17" s="3">
         <v>136800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>145000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>144900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>167700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>151700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>154300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>164000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>169300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>159200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>153000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>147600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>125400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>89500</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1348,65 +1374,68 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E18" s="3">
         <v>14000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>27900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>19600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>19700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>30300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>27300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>25100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>36100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>40000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>12700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>13000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>17700</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1416,8 +1445,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1442,53 +1474,54 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3100</v>
       </c>
-      <c r="G20" s="3">
-        <v>-1100</v>
-      </c>
       <c r="H20" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="I20" s="3">
         <v>2100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>37600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>27400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-17300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-24200</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1498,8 +1531,8 @@
       <c r="T20" s="3">
         <v>0</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
@@ -1510,65 +1543,68 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E21" s="3">
         <v>18500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>34700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>17400</v>
       </c>
-      <c r="G21" s="3">
-        <v>24300</v>
-      </c>
       <c r="H21" s="3">
+        <v>28600</v>
+      </c>
+      <c r="I21" s="3">
         <v>21400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>32000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>29600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>47200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>58700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>37200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-17200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>45800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>18400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>17900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>22400</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,133 +1614,139 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E22" s="3">
         <v>15000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>11000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>18800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>13700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>18300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>10400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>9900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>11200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>10100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>11500</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-7800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>19200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>17100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-19600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>30200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>43600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>24000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-33500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>28900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6200</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1714,76 +1756,82 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-4400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1300</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1850,65 +1898,68 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-6300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>17100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>13000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-15200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>31600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>40600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>16900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-30200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>23100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4900</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1918,65 +1969,68 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-6300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>17100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>13000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-15200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>31600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>40600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-30200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>23100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4900</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1986,8 +2040,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2054,8 +2111,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2122,8 +2182,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2190,8 +2253,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2258,53 +2324,56 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E32" s="3">
         <v>1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3100</v>
       </c>
-      <c r="G32" s="3">
-        <v>1100</v>
-      </c>
       <c r="H32" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-2100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-37600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-27400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>17300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>24200</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2314,8 +2383,8 @@
       <c r="T32" s="3">
         <v>0</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
@@ -2326,65 +2395,68 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-6300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>17100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>13000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-15200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>31600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>40600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-18000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-30200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>23100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4900</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2394,8 +2466,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2462,65 +2537,68 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-6300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>17100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>13000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-15200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>31600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>40600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-18000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-30200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>23100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4900</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2530,70 +2608,73 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45564</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45200</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45109</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45018</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44836</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44745</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44654</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44374</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44283</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43918</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2603,8 +2684,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2629,8 +2713,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2655,53 +2740,54 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E41" s="3">
         <v>50800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>53100</v>
-      </c>
-      <c r="F41" s="3">
-        <v>41100</v>
       </c>
       <c r="G41" s="3">
         <v>41100</v>
       </c>
       <c r="H41" s="3">
+        <v>41100</v>
+      </c>
+      <c r="I41" s="3">
         <v>36800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>42700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>26200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>30600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>44100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>36300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>53900</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2723,8 +2809,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2791,53 +2880,56 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>36100</v>
+      </c>
+      <c r="E43" s="3">
         <v>44500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>56100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>48700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>48400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>47400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>57100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>56300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>47100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>59700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>58200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>63700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>51400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>55400</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2853,59 +2945,62 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>192500</v>
+      </c>
+      <c r="E44" s="3">
         <v>179300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>173500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>184000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>192300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>207200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>217500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>229000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>233600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>230500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>214900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>191100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>185000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>164300</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2921,26 +3016,29 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
+      <c r="W44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>7700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2100</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2953,27 +3051,27 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>18200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>18500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>19000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8900</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,53 +3093,56 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>297300</v>
+      </c>
+      <c r="E46" s="3">
         <v>298600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>301100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>289800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>297400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>304700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>333300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>324200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>325000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>325300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>320500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>314300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>291700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>282600</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3063,34 +3164,37 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3">
         <v>1200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1100</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3">
         <v>3200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2100</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3122,8 +3226,8 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
+      <c r="V47" s="3">
+        <v>0</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
@@ -3131,53 +3235,56 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E48" s="3">
         <v>73600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>73300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>74900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>76500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>78400</v>
-      </c>
-      <c r="I48" s="3">
-        <v>78700</v>
       </c>
       <c r="J48" s="3">
         <v>78700</v>
       </c>
       <c r="K48" s="3">
+        <v>78700</v>
+      </c>
+      <c r="L48" s="3">
         <v>81700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>86000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>88800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>88000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>51500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>50400</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3193,59 +3300,62 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>759000</v>
+      </c>
+      <c r="E49" s="3">
         <v>812000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>822500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>826000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>829500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>832800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>836700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>839400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>843000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>845700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>851500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>846400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>849800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>803700</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3261,14 +3371,17 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3335,8 +3448,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3403,8 +3519,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3444,8 +3563,8 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
         <v>0</v>
@@ -3471,8 +3590,11 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3539,53 +3661,56 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1133300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1184200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1198100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1191700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1203300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1219100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1250700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1242300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1249600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1257100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1260800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1248700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1193100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1136700</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,8 +3732,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3633,8 +3761,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3659,53 +3788,54 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>44800</v>
+      </c>
+      <c r="E57" s="3">
         <v>52700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>58600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>50300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>43700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>39800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>43800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>37400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>44900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>43500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>39600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>41900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>45700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>46600</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3721,59 +3851,62 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E58" s="3">
         <v>11800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6000</v>
-      </c>
-      <c r="M58" s="3">
-        <v>6300</v>
       </c>
       <c r="N58" s="3">
         <v>6300</v>
       </c>
       <c r="O58" s="3">
+        <v>6300</v>
+      </c>
+      <c r="P58" s="3">
         <v>7900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5500</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3795,53 +3928,56 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E59" s="3">
         <v>12800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>14000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>18400</v>
       </c>
-      <c r="G59" s="3">
-        <v>16100</v>
-      </c>
       <c r="H59" s="3">
+        <v>12700</v>
+      </c>
+      <c r="I59" s="3">
         <v>9800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>49300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>46900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>44900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>48600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>38200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>49400</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,53 +3999,56 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>95200</v>
+      </c>
+      <c r="E60" s="3">
         <v>101900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>107500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>101700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>93700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>88900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>103200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>95600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>101300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>96400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>90800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>96800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>91800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>101600</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3931,53 +4070,56 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>577300</v>
+      </c>
+      <c r="E61" s="3">
         <v>576700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>575100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>585400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>603100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>629500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>654000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>662900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>643600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>635600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>636800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>636300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>637700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>570400</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3999,53 +4141,56 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E62" s="3">
         <v>2000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>13100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>88800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>106800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>148800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>176100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>159100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>144900</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4061,14 +4206,17 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4135,8 +4283,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4203,8 +4354,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4271,53 +4425,56 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>712200</v>
+      </c>
+      <c r="E66" s="3">
         <v>725500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>734900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>746800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>762200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>781200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>815300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>821900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>833700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>838800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>876400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>909200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>888600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>816900</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4339,8 +4496,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4365,8 +4525,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4433,8 +4594,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4501,8 +4665,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4569,8 +4736,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4637,53 +4807,56 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E72" s="3">
         <v>82500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>88800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>71700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>68000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>66800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>66000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>53000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>48800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>64000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>32400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-8100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-25000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4705,8 +4878,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4773,8 +4949,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4841,8 +5020,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4909,53 +5091,56 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>421200</v>
+      </c>
+      <c r="E76" s="3">
         <v>458700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>463200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>444900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>441200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>437900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>435400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>420400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>416000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>418300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>384400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>339400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>304500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>319800</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4977,8 +5162,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5045,70 +5233,73 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45564</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45200</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45109</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45018</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44836</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44745</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44654</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44374</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44283</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43918</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5118,65 +5309,68 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-37800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-6300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>17100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>13000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-15200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>31600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>40600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-18000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-30200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>23100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4900</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5186,8 +5380,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5212,67 +5409,68 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4700</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -5280,8 +5478,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5348,8 +5549,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5416,8 +5620,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5484,8 +5691,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5552,8 +5762,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5620,65 +5833,68 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>25700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>18800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>31200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>22500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>30700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>18300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>27400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>19000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>12800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>17600</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5688,8 +5904,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5714,67 +5933,68 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-1700</v>
       </c>
       <c r="I91" s="3">
         <v>-1700</v>
       </c>
       <c r="J91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1300</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -5782,8 +6002,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5850,8 +6073,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5918,67 +6144,70 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-16200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-62200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-57800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-158900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1300</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -5986,8 +6215,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6012,8 +6244,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6038,8 +6271,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6080,8 +6313,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6148,8 +6384,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6216,8 +6455,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6284,65 +6526,68 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-12400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-17700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-26000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-27400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-3300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>47900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>30800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>163000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>27500</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6352,47 +6597,50 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6405,8 +6653,8 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -6420,65 +6668,68 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12000</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>4200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>21900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>9500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-17600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-31800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>15800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>16900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>43800</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6486,6 +6737,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
   <si>
     <t>HLLY</t>
   </si>
@@ -656,99 +656,100 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45564</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45200</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45109</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45018</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44836</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44745</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44654</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44465</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44374</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44283</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43918</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -758,139 +759,145 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>153000</v>
+      </c>
+      <c r="E8" s="3">
         <v>140100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>134000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>169500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>158600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>155700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>156500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>175300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>172200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>154200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>154800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>179400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>200100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>179800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>159700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>193000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>160300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>138400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>107200</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>89000</v>
+      </c>
+      <c r="E9" s="3">
         <v>68000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>81700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>99200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>106600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>95500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>98200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>105500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>104500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>106900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>106400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>104100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>117300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>105100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>94500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>111800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>94700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>83900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>63800</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -900,68 +907,71 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>64100</v>
+      </c>
+      <c r="E10" s="3">
         <v>72100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>52300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>70300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>52100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>60300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>58400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>69700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>67700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>47300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>48400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>75300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>82800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>74700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>65200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>81200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>65600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>54500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>43400</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -971,8 +981,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -998,68 +1011,69 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E12" s="3">
         <v>5000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>6100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6200</v>
-      </c>
-      <c r="K12" s="3">
-        <v>6700</v>
       </c>
       <c r="L12" s="3">
         <v>6700</v>
       </c>
       <c r="M12" s="3">
+        <v>6700</v>
+      </c>
+      <c r="N12" s="3">
         <v>6000</v>
-      </c>
-      <c r="N12" s="3">
-        <v>8200</v>
       </c>
       <c r="O12" s="3">
         <v>8200</v>
       </c>
       <c r="P12" s="3">
+        <v>8200</v>
+      </c>
+      <c r="Q12" s="3">
         <v>8100</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>7100</v>
       </c>
       <c r="R12" s="3">
         <v>7100</v>
       </c>
       <c r="S12" s="3">
+        <v>7100</v>
+      </c>
+      <c r="T12" s="3">
         <v>6000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5600</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1069,8 +1083,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1140,68 +1157,71 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
         <v>51500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>14000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>25000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>4300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>19700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>7500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1211,16 +1231,19 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E15" s="3">
         <v>3600</v>
-      </c>
-      <c r="E15" s="3">
-        <v>3400</v>
       </c>
       <c r="F15" s="3">
         <v>3400</v>
@@ -1229,10 +1252,10 @@
         <v>3400</v>
       </c>
       <c r="H15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I15" s="3">
         <v>3500</v>
-      </c>
-      <c r="I15" s="3">
-        <v>3700</v>
       </c>
       <c r="J15" s="3">
         <v>3700</v>
@@ -1253,37 +1276,40 @@
         <v>3700</v>
       </c>
       <c r="P15" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="Q15" s="3">
         <v>3600</v>
       </c>
       <c r="R15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="S15" s="3">
         <v>3500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2700</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1306,68 +1332,69 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>133200</v>
+      </c>
+      <c r="E17" s="3">
         <v>109900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>120000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>141600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>147800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>136200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>136800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>145000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>144900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>167700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>151700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>154300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>164000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>169300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>159200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>153000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>147600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>125400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>89500</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1377,68 +1404,71 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>19800</v>
+      </c>
+      <c r="E18" s="3">
         <v>30100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>14000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>27900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>10800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>19600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>19700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>30300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>27300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>25100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>36100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>40000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>17700</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1448,8 +1478,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1475,56 +1508,57 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E20" s="3">
         <v>7600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>37600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>27400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-24200</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1534,8 +1568,8 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3">
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
@@ -1546,68 +1580,71 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E21" s="3">
         <v>26100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>18500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>34700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>17400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>28600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>21400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>32000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>29600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>47200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>58700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>37200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-17200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>45800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>18400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>17900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>22400</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1617,139 +1654,145 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E22" s="3">
         <v>11500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>11000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>18800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>13700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>18300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>9900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>10100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>11900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>11500</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-40500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-7800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>19200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>17100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-19600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>30200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>43600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>24000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-14800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-33500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>28900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6200</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1759,79 +1802,85 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-2700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-4400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-3300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1300</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="X24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1901,68 +1950,71 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-37800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-6300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>13000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-15200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>31600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>40600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>16900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-30200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>23100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4900</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1972,68 +2024,71 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-37800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-6300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>17100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>13000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-15200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>31600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>40600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>16900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-30200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>23100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4900</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2043,8 +2098,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2114,8 +2172,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2185,8 +2246,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2256,8 +2320,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2327,56 +2394,59 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-7600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-37600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-27400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>17300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>24200</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -2386,8 +2456,8 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3">
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
@@ -2398,68 +2468,71 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-37800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>13000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-15200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>31600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>40600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>16900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-30200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>23100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4900</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2469,8 +2542,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2540,68 +2616,71 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-37800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>13000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-15200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>31600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>40600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>16900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-30200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>23100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4900</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2611,73 +2690,76 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45564</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45200</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45109</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45018</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44836</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44745</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44654</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44465</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44374</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44283</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43918</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2687,8 +2769,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2714,8 +2799,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2741,56 +2827,57 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E41" s="3">
         <v>56100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>50800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>53100</v>
-      </c>
-      <c r="G41" s="3">
-        <v>41100</v>
       </c>
       <c r="H41" s="3">
         <v>41100</v>
       </c>
       <c r="I41" s="3">
+        <v>41100</v>
+      </c>
+      <c r="J41" s="3">
         <v>36800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>42700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>20800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>26200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>30600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>44100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>36300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>53900</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2812,8 +2899,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2883,56 +2973,59 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E43" s="3">
         <v>36100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>44500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>56100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>48700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>48400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>47400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>57100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>56300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>47100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>59700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>58200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>63700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>51400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>55400</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2948,62 +3041,65 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
+      <c r="X43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>189100</v>
+      </c>
+      <c r="E44" s="3">
         <v>192500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>179300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>173500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>184000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>192300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>207200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>217500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>229000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>233600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>230500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>214900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>191100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>185000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>164300</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3019,29 +3115,32 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
+      <c r="X44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3">
         <v>7700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2100</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3054,27 +3153,27 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>18200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>18500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>15400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>19000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8900</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3096,56 +3195,59 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>288200</v>
+      </c>
+      <c r="E46" s="3">
         <v>297300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>298600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>301100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>289800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>297400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>304700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>333300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>324200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>325000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>325300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>320500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>314300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>291700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>282600</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3167,8 +3269,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3178,26 +3283,26 @@
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3">
         <v>1200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1100</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>3200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2100</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3229,8 +3334,8 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
+      <c r="W47" s="3">
+        <v>0</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
@@ -3238,56 +3343,59 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>76500</v>
+      </c>
+      <c r="E48" s="3">
         <v>77000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>73600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>73300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>74900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>76500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>78400</v>
-      </c>
-      <c r="J48" s="3">
-        <v>78700</v>
       </c>
       <c r="K48" s="3">
         <v>78700</v>
       </c>
       <c r="L48" s="3">
+        <v>78700</v>
+      </c>
+      <c r="M48" s="3">
         <v>81700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>86000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>88800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>88000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>51500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>50400</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3303,62 +3411,65 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>779500</v>
+      </c>
+      <c r="E49" s="3">
         <v>759000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>812000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>822500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>826000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>829500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>832800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>836700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>839400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>843000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>845700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>851500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>846400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>849800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>803700</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3374,14 +3485,17 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3451,8 +3565,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3522,8 +3639,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3566,8 +3686,8 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -3593,8 +3713,11 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3664,56 +3787,59 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1144200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1133300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1184200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1198100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1191700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1203300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1219100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1250700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1242300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1249600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1257100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1260800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1248700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1193100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1136700</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3735,8 +3861,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3762,8 +3891,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3789,56 +3919,57 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E57" s="3">
         <v>44800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>52700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>58600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>50300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>43700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>39800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>43800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>37400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>44900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>43500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>39600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>41900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>45700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>46600</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3854,62 +3985,65 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
+      <c r="X57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E58" s="3">
         <v>12500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>6300</v>
       </c>
       <c r="O58" s="3">
         <v>6300</v>
       </c>
       <c r="P58" s="3">
+        <v>6300</v>
+      </c>
+      <c r="Q58" s="3">
         <v>7900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5500</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3931,56 +4065,59 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E59" s="3">
         <v>16300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>49300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>46900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>44900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>48600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>38200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>49400</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4002,56 +4139,59 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>100800</v>
+      </c>
+      <c r="E60" s="3">
         <v>95200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>101900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>107500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>101700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>93700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>88900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>103200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>95600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>101300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>96400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>90800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>96800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>91800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>101600</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4073,56 +4213,59 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>578800</v>
+      </c>
+      <c r="E61" s="3">
         <v>577300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>576700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>575100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>585400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>603100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>629500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>654000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>662900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>643600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>635600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>636800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>636300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>637700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>570400</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4144,56 +4287,59 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E62" s="3">
         <v>2300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>88800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>106800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>148800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>176100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>159100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>144900</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4209,14 +4355,17 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4286,8 +4435,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4357,8 +4509,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4428,56 +4583,59 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>719600</v>
+      </c>
+      <c r="E66" s="3">
         <v>712200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>725500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>734900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>746800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>762200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>781200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>815300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>821900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>833700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>838800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>876400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>909200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>888600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>816900</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4499,8 +4657,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4526,8 +4687,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4597,8 +4759,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4668,8 +4833,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4739,8 +4907,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4810,56 +4981,59 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>47600</v>
+      </c>
+      <c r="E72" s="3">
         <v>44700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>82500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>88800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>71700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>68000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>66800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>66000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>53000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>48800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>64000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>32400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-8100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-7000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4881,8 +5055,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4952,8 +5129,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5023,8 +5203,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5094,56 +5277,59 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>424600</v>
+      </c>
+      <c r="E76" s="3">
         <v>421200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>458700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>463200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>444900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>441200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>437900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>435400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>420400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>416000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>418300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>384400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>339400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>304500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>319800</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5165,8 +5351,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5236,73 +5425,76 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45564</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45200</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45109</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45018</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44836</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44745</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44654</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44465</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44374</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44283</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43918</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5312,68 +5504,71 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-37800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>13000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-15200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>31600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>40600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>16900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-30200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>23100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4900</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5383,8 +5578,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5410,70 +5608,71 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E83" s="3">
         <v>4000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>4800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4700</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -5481,8 +5680,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5552,8 +5754,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5623,8 +5828,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5694,8 +5902,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5765,8 +5976,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5836,68 +6050,71 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E89" s="3">
         <v>4100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>25700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>18800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>31200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>22500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>30700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>18300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-21500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>27400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>19000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>12800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>17600</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5907,8 +6124,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5934,70 +6154,71 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-1700</v>
       </c>
       <c r="J91" s="3">
         <v>-1700</v>
       </c>
       <c r="K91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1300</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -6005,8 +6226,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6076,8 +6300,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6147,70 +6374,73 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E94" s="3">
         <v>4700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-16200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-7200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-62200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-57800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-158900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1300</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -6218,8 +6448,11 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6245,8 +6478,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6274,8 +6508,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6316,8 +6550,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6387,8 +6624,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6458,8 +6698,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6529,68 +6772,71 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-12400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-17700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-26000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-27400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>8300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-3300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>47900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>30800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>163000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>27500</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6600,50 +6846,53 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6656,8 +6905,8 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -6671,68 +6920,71 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E102" s="3">
         <v>5300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12000</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>4200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>21900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>7800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-31800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>15800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>16900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>43800</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6740,6 +6992,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
   <si>
     <t>HLLY</t>
   </si>
@@ -656,103 +656,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E7" s="2">
         <v>45746</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45564</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45200</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45109</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45018</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44836</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44745</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44654</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44465</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44374</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44283</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43918</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -762,145 +763,151 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>166700</v>
+      </c>
+      <c r="E8" s="3">
         <v>153000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>140100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>134000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>169500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>158600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>155700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>156500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>175300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>172200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>154200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>154800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>179400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>200100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>179800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>159700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>193000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>160300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>138400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>107200</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>97100</v>
+      </c>
+      <c r="E9" s="3">
         <v>89000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>68000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>81700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>99200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>106600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>95500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>98200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>105500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>104500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>106900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>106400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>104100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>117300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>105100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>94500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>111800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>94700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>83900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>63800</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
@@ -910,71 +917,74 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E10" s="3">
         <v>64100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>72100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>52300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>70300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>52100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>60300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>58400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>69700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>67700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>47300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>48400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>75300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>82800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>74700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>65200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>81200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>65600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>54500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>43400</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
@@ -984,8 +994,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1012,71 +1025,72 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E12" s="3">
         <v>4100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>6100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>6200</v>
-      </c>
-      <c r="L12" s="3">
-        <v>6700</v>
       </c>
       <c r="M12" s="3">
         <v>6700</v>
       </c>
       <c r="N12" s="3">
+        <v>6700</v>
+      </c>
+      <c r="O12" s="3">
         <v>6000</v>
-      </c>
-      <c r="O12" s="3">
-        <v>8200</v>
       </c>
       <c r="P12" s="3">
         <v>8200</v>
       </c>
       <c r="Q12" s="3">
+        <v>8200</v>
+      </c>
+      <c r="R12" s="3">
         <v>8100</v>
-      </c>
-      <c r="R12" s="3">
-        <v>7100</v>
       </c>
       <c r="S12" s="3">
         <v>7100</v>
       </c>
       <c r="T12" s="3">
+        <v>7100</v>
+      </c>
+      <c r="U12" s="3">
         <v>6000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6300</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5600</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1086,8 +1100,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1160,71 +1177,74 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>51500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>14000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>25000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>4300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>19700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>7500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2300</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1234,19 +1254,22 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E15" s="3">
         <v>3500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3600</v>
-      </c>
-      <c r="F15" s="3">
-        <v>3400</v>
       </c>
       <c r="G15" s="3">
         <v>3400</v>
@@ -1255,10 +1278,10 @@
         <v>3400</v>
       </c>
       <c r="I15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="J15" s="3">
         <v>3500</v>
-      </c>
-      <c r="J15" s="3">
-        <v>3700</v>
       </c>
       <c r="K15" s="3">
         <v>3700</v>
@@ -1279,37 +1302,40 @@
         <v>3700</v>
       </c>
       <c r="Q15" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="R15" s="3">
         <v>3600</v>
       </c>
       <c r="S15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="T15" s="3">
         <v>3500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2700</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y15" s="3">
-        <v>0</v>
+      <c r="Y15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1333,71 +1359,72 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>138800</v>
+      </c>
+      <c r="E17" s="3">
         <v>133200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>109900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>120000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>141600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>147800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>136200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>136800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>145000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>144900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>167700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>151700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>154300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>164000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>169300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>159200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>153000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>147600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>125400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>89500</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1407,71 +1434,74 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E18" s="3">
         <v>19800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>30100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>14000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>27900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>10800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>19600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>19700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>30300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>27300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>25100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>36100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>40000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17700</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1481,8 +1511,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1509,59 +1542,60 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>7600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>37600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>27400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-17300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-24200</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1571,8 +1605,8 @@
       <c r="V20" s="3">
         <v>0</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
@@ -1583,71 +1617,74 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E21" s="3">
         <v>23400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>26100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>18500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>34700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>17400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>28600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>21400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>32000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>29600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>47200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>58700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>37200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-17200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>45800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>18400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>17900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>22400</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1657,145 +1694,151 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E22" s="3">
         <v>15700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>11500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>13200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>18300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>10400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>9000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>9900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>10100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>11900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>11500</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E23" s="3">
         <v>3900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-40500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>19200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>17100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-19600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>30200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>43600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>24000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-14800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-33500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>28900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6200</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1805,82 +1848,88 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E24" s="3">
         <v>1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-2700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-4400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-3300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1300</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1953,71 +2002,74 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E26" s="3">
         <v>2800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-37800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>13000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>31600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>40600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>16900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-18000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-30200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>23100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4900</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2027,71 +2079,74 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E27" s="3">
         <v>2800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-37800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>13000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>31600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>40600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>16900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-18000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-30200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>23100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4900</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2101,8 +2156,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2175,8 +2233,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2249,8 +2310,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2323,8 +2387,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2397,59 +2464,62 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-7600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-37600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-27400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>17300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>24200</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2459,8 +2529,8 @@
       <c r="V32" s="3">
         <v>0</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
@@ -2471,71 +2541,74 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E33" s="3">
         <v>2800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-37800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>13000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>31600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>40600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>16900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-18000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-30200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>23100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4900</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2618,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2619,71 +2695,74 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E35" s="3">
         <v>2800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-37800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>13000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>31600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>40600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>16900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-18000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-30200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>23100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4900</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2693,76 +2772,79 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E38" s="2">
         <v>45746</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45564</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45200</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45109</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45018</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44836</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44745</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44654</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44465</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44374</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44283</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43918</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2772,8 +2854,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2800,8 +2885,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2828,59 +2914,60 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>63800</v>
+      </c>
+      <c r="E41" s="3">
         <v>39100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>56100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>50800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>53100</v>
-      </c>
-      <c r="H41" s="3">
-        <v>41100</v>
       </c>
       <c r="I41" s="3">
         <v>41100</v>
       </c>
       <c r="J41" s="3">
+        <v>41100</v>
+      </c>
+      <c r="K41" s="3">
         <v>36800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>42700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>20800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>30600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>44100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>36300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>53900</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2902,8 +2989,11 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2976,59 +3066,62 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E43" s="3">
         <v>50900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>36100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>44500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>56100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>48700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>48400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>47400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>57100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>56300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>47100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>59700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>58200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>63700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>51400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>55400</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3044,65 +3137,68 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>180800</v>
+      </c>
+      <c r="E44" s="3">
         <v>189100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>192500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>179300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>173500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>184000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>192300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>207200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>217500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>229000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>233600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>230500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>214900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>191100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>185000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>164300</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3118,14 +3214,17 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3135,15 +3234,15 @@
       <c r="E45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
         <v>7700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2100</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3156,27 +3255,27 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3">
         <v>18200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>18500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>15400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>19000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8900</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3198,59 +3297,62 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>303200</v>
+      </c>
+      <c r="E46" s="3">
         <v>288200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>297300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>298600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>301100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>289800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>297400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>304700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>333300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>324200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>325000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>325300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>320500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>314300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>291700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>282600</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3272,8 +3374,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3286,26 +3391,26 @@
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3">
         <v>1200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1100</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>3200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3337,8 +3442,8 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
+      <c r="X47" s="3">
+        <v>0</v>
       </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
@@ -3346,59 +3451,62 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E48" s="3">
         <v>76500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>77000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>73600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>73300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>74900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>76500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>78400</v>
-      </c>
-      <c r="K48" s="3">
-        <v>78700</v>
       </c>
       <c r="L48" s="3">
         <v>78700</v>
       </c>
       <c r="M48" s="3">
+        <v>78700</v>
+      </c>
+      <c r="N48" s="3">
         <v>81700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>86000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>88800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>88000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>51500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>50400</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3414,65 +3522,68 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>776100</v>
+      </c>
+      <c r="E49" s="3">
         <v>779500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>759000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>812000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>822500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>826000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>829500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>832800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>836700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>839400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>843000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>845700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>851500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>846400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>849800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>803700</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3488,14 +3599,17 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3568,8 +3682,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3642,8 +3759,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3689,8 +3809,8 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -3716,8 +3836,11 @@
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3790,59 +3913,62 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1158200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1144200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1133300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1184200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1198100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1191700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1203300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1219100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1250700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1242300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1249600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1257100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1260800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1248700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1193100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1136700</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,8 +3990,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3892,8 +4021,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3920,59 +4050,60 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E57" s="3">
         <v>37600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>44800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>52700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>58600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>50300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>43700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>39800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>43800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>37400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>44900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>43500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>39600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>41900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>45700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>46600</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3988,65 +4119,68 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E58" s="3">
         <v>12300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>6300</v>
       </c>
       <c r="P58" s="3">
         <v>6300</v>
       </c>
       <c r="Q58" s="3">
+        <v>6300</v>
+      </c>
+      <c r="R58" s="3">
         <v>7900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5500</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,59 +4202,62 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E59" s="3">
         <v>12200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>18400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>14900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>49300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>46900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>44900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>48600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>38200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>49400</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4142,59 +4279,62 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>103600</v>
+      </c>
+      <c r="E60" s="3">
         <v>100800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>95200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>101900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>107500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>101700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>93700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>88900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>103200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>95600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>101300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>96400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>90800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>96800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>91800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>101600</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4216,59 +4356,62 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>578700</v>
+      </c>
+      <c r="E61" s="3">
         <v>578800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>577300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>576700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>575100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>585400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>603100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>629500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>654000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>662900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>643600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>635600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>636800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>636300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>637700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>570400</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4290,59 +4433,62 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E62" s="3">
         <v>2600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>88800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>106800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>148800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>176100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>159100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>144900</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4358,14 +4504,17 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4438,8 +4587,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4512,8 +4664,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4586,59 +4741,62 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>720400</v>
+      </c>
+      <c r="E66" s="3">
         <v>719600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>712200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>725500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>734900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>746800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>762200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>781200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>815300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>821900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>833700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>838800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>876400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>909200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>888600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>816900</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4660,8 +4818,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4688,8 +4849,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4762,8 +4924,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4836,8 +5001,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4910,8 +5078,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4984,59 +5155,62 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>58400</v>
+      </c>
+      <c r="E72" s="3">
         <v>47600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>44700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>82500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>88800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>71700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>68000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>66800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>66000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>53000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>48800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>64000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>32400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-25000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-7000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5058,8 +5232,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5132,8 +5309,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5206,8 +5386,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5280,59 +5463,62 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>437800</v>
+      </c>
+      <c r="E76" s="3">
         <v>424600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>421200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>458700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>463200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>444900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>441200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>437900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>435400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>420400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>416000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>418300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>384400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>339400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>304500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>319800</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5354,8 +5540,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5428,76 +5617,79 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E80" s="2">
         <v>45746</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45564</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45200</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45109</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45018</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44836</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44745</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44654</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44465</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44374</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44283</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43918</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5507,71 +5699,74 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E81" s="3">
         <v>2800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-37800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>13000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>31600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>40600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>16900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-18000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-30200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>23100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4900</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5581,8 +5776,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5609,73 +5807,74 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E83" s="3">
         <v>3900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>4800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4700</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -5683,8 +5882,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5757,8 +5959,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5831,8 +6036,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5905,8 +6113,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5979,8 +6190,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6053,71 +6267,74 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>25700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>18800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>31200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>22500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>30700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>18300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-21500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>27400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>19000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>12800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>17600</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6127,8 +6344,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6155,73 +6375,74 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-1700</v>
       </c>
       <c r="K91" s="3">
         <v>-1700</v>
       </c>
       <c r="L91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1300</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -6229,8 +6450,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6303,8 +6527,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6377,73 +6604,76 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>4700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-16200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-62200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-57800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-158900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1300</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -6451,8 +6681,11 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6479,8 +6712,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6511,8 +6745,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -6553,8 +6787,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6627,8 +6864,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6701,8 +6941,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6775,71 +7018,74 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-12400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-17700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-26000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-27400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-8400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>8300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>47900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>30800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>163000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>27500</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6849,8 +7095,11 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6858,44 +7107,44 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6908,8 +7157,8 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -6923,71 +7172,74 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12000</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>4200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>21900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>7800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-17600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-31800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>15800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>16900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>43800</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6995,6 +7247,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
   <si>
     <t>HLLY</t>
   </si>
@@ -656,111 +656,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45928</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45837</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45746</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45564</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45200</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45109</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45018</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44836</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44745</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44654</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44374</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44283</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43918</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
@@ -770,157 +770,163 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>155400</v>
+      </c>
+      <c r="E8" s="3">
         <v>138400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>166700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>153000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>140100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>134000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>169500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>158600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>155700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>156500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>175300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>172200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>154200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>154800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>179400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>200100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>179800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>159700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>193000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>160300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>138400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>107200</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA8" s="3">
-        <v>0</v>
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>82700</v>
+      </c>
+      <c r="E9" s="3">
         <v>78500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>97100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>89000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>68000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>81700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>99200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>106600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>95500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>98200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>105500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>104500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>106900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>106400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>104100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>117300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>105100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>94500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>111800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>94700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>83900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>63800</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
@@ -930,77 +936,80 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>72800</v>
+      </c>
+      <c r="E10" s="3">
         <v>59800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>69600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>64100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>72100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>52300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>70300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>52100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>60300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>58400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>69700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>67700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>47300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>48400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>75300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>82800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>74700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>65200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>81200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>65600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>54500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>43400</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1010,8 +1019,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1040,77 +1052,78 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E12" s="3">
         <v>4700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>6100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6200</v>
-      </c>
-      <c r="N12" s="3">
-        <v>6700</v>
       </c>
       <c r="O12" s="3">
         <v>6700</v>
       </c>
       <c r="P12" s="3">
+        <v>6700</v>
+      </c>
+      <c r="Q12" s="3">
         <v>6000</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>8200</v>
       </c>
       <c r="R12" s="3">
         <v>8200</v>
       </c>
       <c r="S12" s="3">
+        <v>8200</v>
+      </c>
+      <c r="T12" s="3">
         <v>8100</v>
-      </c>
-      <c r="T12" s="3">
-        <v>7100</v>
       </c>
       <c r="U12" s="3">
         <v>7100</v>
       </c>
       <c r="V12" s="3">
+        <v>7100</v>
+      </c>
+      <c r="W12" s="3">
         <v>6000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>6300</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5600</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1120,8 +1133,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1200,77 +1216,80 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E14" s="3">
         <v>2500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
-        <v>51500</v>
-      </c>
       <c r="H14" s="3">
+        <v>53300</v>
+      </c>
+      <c r="I14" s="3">
         <v>7800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>14000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>25000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>4300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>19700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>7500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2300</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1280,25 +1299,28 @@
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E15" s="3">
         <v>3500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3600</v>
-      </c>
-      <c r="H15" s="3">
-        <v>3400</v>
       </c>
       <c r="I15" s="3">
         <v>3400</v>
@@ -1307,10 +1329,10 @@
         <v>3400</v>
       </c>
       <c r="K15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L15" s="3">
         <v>3500</v>
-      </c>
-      <c r="L15" s="3">
-        <v>3700</v>
       </c>
       <c r="M15" s="3">
         <v>3700</v>
@@ -1331,37 +1353,40 @@
         <v>3700</v>
       </c>
       <c r="S15" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="T15" s="3">
         <v>3600</v>
       </c>
       <c r="U15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="V15" s="3">
         <v>3500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2700</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1387,77 +1412,78 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E17" s="3">
         <v>121100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>138800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>133200</v>
       </c>
-      <c r="G17" s="3">
-        <v>109900</v>
-      </c>
       <c r="H17" s="3">
+        <v>110500</v>
+      </c>
+      <c r="I17" s="3">
         <v>120000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>141600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>147800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>136200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>136800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>145000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>144900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>167700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>151700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>154300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>164000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>169300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>159200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>153000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>147600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>125400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>89500</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1467,77 +1493,80 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E18" s="3">
         <v>17200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>27900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>19800</v>
       </c>
-      <c r="G18" s="3">
-        <v>30100</v>
-      </c>
       <c r="H18" s="3">
+        <v>29500</v>
+      </c>
+      <c r="I18" s="3">
         <v>14000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>27900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>19600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>30300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>27300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-13500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>25100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>36100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>40000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>12700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>13000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>17700</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1547,8 +1576,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1577,65 +1609,66 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>3000</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>7600</v>
-      </c>
       <c r="H20" s="3">
+        <v>5200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>37600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>27400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-17300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-24200</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -1645,8 +1678,8 @@
       <c r="X20" s="3">
         <v>0</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
+      <c r="Y20" s="3">
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
@@ -1657,77 +1690,80 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E21" s="3">
         <v>17700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>31200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>23400</v>
       </c>
-      <c r="G21" s="3">
-        <v>26100</v>
-      </c>
       <c r="H21" s="3">
+        <v>27900</v>
+      </c>
+      <c r="I21" s="3">
         <v>18500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>34700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>17400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>28600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>21400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>32000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>29600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>47200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>58700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>37200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-17200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>45800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>18400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>17900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>22400</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,8 +1773,11 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1746,148 +1785,151 @@
         <v>11300</v>
       </c>
       <c r="E22" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F22" s="3">
         <v>13400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>15700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
+        <v>11300</v>
+      </c>
+      <c r="I22" s="3">
+        <v>17200</v>
+      </c>
+      <c r="J22" s="3">
+        <v>13200</v>
+      </c>
+      <c r="K22" s="3">
+        <v>11000</v>
+      </c>
+      <c r="L22" s="3">
+        <v>18800</v>
+      </c>
+      <c r="M22" s="3">
+        <v>13700</v>
+      </c>
+      <c r="N22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="O22" s="3">
+        <v>18300</v>
+      </c>
+      <c r="P22" s="3">
+        <v>13400</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>10400</v>
+      </c>
+      <c r="R22" s="3">
+        <v>9000</v>
+      </c>
+      <c r="S22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="T22" s="3">
+        <v>8000</v>
+      </c>
+      <c r="U22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="V22" s="3">
+        <v>11200</v>
+      </c>
+      <c r="W22" s="3">
+        <v>10100</v>
+      </c>
+      <c r="X22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="Y22" s="3">
         <v>11500</v>
       </c>
-      <c r="H22" s="3">
-        <v>15000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>13200</v>
-      </c>
-      <c r="J22" s="3">
-        <v>11000</v>
-      </c>
-      <c r="K22" s="3">
-        <v>18800</v>
-      </c>
-      <c r="L22" s="3">
-        <v>13700</v>
-      </c>
-      <c r="M22" s="3">
-        <v>9900</v>
-      </c>
-      <c r="N22" s="3">
-        <v>18300</v>
-      </c>
-      <c r="O22" s="3">
-        <v>13400</v>
-      </c>
-      <c r="P22" s="3">
-        <v>10400</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>9000</v>
-      </c>
-      <c r="R22" s="3">
-        <v>7400</v>
-      </c>
-      <c r="S22" s="3">
-        <v>8000</v>
-      </c>
-      <c r="T22" s="3">
-        <v>9900</v>
-      </c>
-      <c r="U22" s="3">
-        <v>11200</v>
-      </c>
-      <c r="V22" s="3">
-        <v>10100</v>
-      </c>
-      <c r="W22" s="3">
-        <v>11900</v>
-      </c>
-      <c r="X22" s="3">
-        <v>11500</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E23" s="3">
         <v>500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>14400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-40500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>19200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>17100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-19600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>30200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>43600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>24000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-14800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-33500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>28900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6200</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1897,88 +1939,94 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E24" s="3">
         <v>1300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-3300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1300</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2057,77 +2105,80 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-37800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>17100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>13000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-15200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>31600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>40600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>16900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-18000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-30200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>23100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4900</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2137,77 +2188,80 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-37800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>17100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>13000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-15200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>31600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>40600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>16900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-18000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-30200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>23100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4900</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2217,8 +2271,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2297,8 +2354,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2377,8 +2437,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2457,8 +2520,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2537,65 +2603,68 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3000</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>-7600</v>
-      </c>
       <c r="H32" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-37600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-27400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>17300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>24200</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -2605,8 +2674,8 @@
       <c r="X32" s="3">
         <v>0</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
+      <c r="Y32" s="3">
+        <v>0</v>
       </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
@@ -2617,77 +2686,80 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-37800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>13000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-15200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>31600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>40600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>16900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-18000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-30200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>23100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4900</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2697,8 +2769,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2777,77 +2852,80 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-37800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>13000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-15200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>31600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>40600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>16900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-18000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-30200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>23100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4900</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2857,82 +2935,85 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45928</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45837</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45746</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45564</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45200</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45109</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45018</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44836</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44745</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44654</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44374</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44283</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43918</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2942,8 +3023,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2972,8 +3056,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3002,65 +3087,66 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>37200</v>
+      </c>
+      <c r="E41" s="3">
         <v>50700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>63800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>39100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>56100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>50800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>53100</v>
-      </c>
-      <c r="J41" s="3">
-        <v>41100</v>
       </c>
       <c r="K41" s="3">
         <v>41100</v>
       </c>
       <c r="L41" s="3">
+        <v>41100</v>
+      </c>
+      <c r="M41" s="3">
         <v>36800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>42700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>20800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>26200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>16600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>30600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>44100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>36300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>53900</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3082,8 +3168,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3162,65 +3251,68 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E43" s="3">
         <v>49600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>51000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>50900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>36100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>44500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>56100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>48700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>48400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>47400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>57100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>56300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>47100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>59700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>58200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>63700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>51400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>55400</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3236,71 +3328,74 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA43" s="3">
-        <v>0</v>
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>205700</v>
+      </c>
+      <c r="E44" s="3">
         <v>195700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>180800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>189100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>192500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>179300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>173500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>184000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>192300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>207200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>217500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>229000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>233600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>230500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>214900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>191100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>185000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>164300</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3316,14 +3411,17 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA44" s="3">
-        <v>0</v>
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3339,15 +3437,15 @@
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3">
         <v>7700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3360,27 +3458,27 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>18200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>18500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>16900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>19000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8900</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3402,65 +3500,68 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>316200</v>
+      </c>
+      <c r="E46" s="3">
         <v>316100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>303200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>288200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>297300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>298600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>301100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>289800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>297400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>304700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>333300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>324200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>325000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>325300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>320500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>314300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>291700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>282600</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3482,8 +3583,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3502,26 +3606,26 @@
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3">
         <v>1200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1100</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>3200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2100</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3553,8 +3657,8 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>3</v>
+      <c r="Z47" s="3">
+        <v>0</v>
       </c>
       <c r="AA47" s="3" t="s">
         <v>3</v>
@@ -3562,65 +3666,68 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>78500</v>
+      </c>
+      <c r="E48" s="3">
         <v>76400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>79000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>76500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>77000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>73600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>73300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>74900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>76500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>78400</v>
-      </c>
-      <c r="M48" s="3">
-        <v>78700</v>
       </c>
       <c r="N48" s="3">
         <v>78700</v>
       </c>
       <c r="O48" s="3">
+        <v>78700</v>
+      </c>
+      <c r="P48" s="3">
         <v>81700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>86000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>88800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>88000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>51500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>50400</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3636,71 +3743,74 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA48" s="3">
-        <v>0</v>
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>769300</v>
+      </c>
+      <c r="E49" s="3">
         <v>772700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>776100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>779500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>759000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>812000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>822500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>826000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>829500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>832800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>836700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>839400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>843000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>845700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>851500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>846400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>849800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>803700</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3716,14 +3826,17 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3802,8 +3915,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3882,8 +3998,11 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3935,8 +4054,8 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -3962,8 +4081,11 @@
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4042,65 +4164,68 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1164000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1165100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1158200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1144200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1133300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1184200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1198100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1191700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1203300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1219100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1250700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1242300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1249600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1257100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1260800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1248700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1193100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1136700</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4122,8 +4247,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4152,8 +4280,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4182,65 +4311,66 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>60100</v>
+      </c>
+      <c r="E57" s="3">
         <v>51200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>44500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>37600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>44800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>52700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>58600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>50300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>43700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>39800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>43800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>37400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>44900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>43500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>39600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>41900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>45700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>46600</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4256,71 +4386,74 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA57" s="3">
-        <v>0</v>
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E58" s="3">
         <v>12200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>6300</v>
       </c>
       <c r="R58" s="3">
         <v>6300</v>
       </c>
       <c r="S58" s="3">
+        <v>6300</v>
+      </c>
+      <c r="T58" s="3">
         <v>7900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5500</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4342,65 +4475,68 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E59" s="3">
         <v>12600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>14000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>18400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>49300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>46900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>44900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>48600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>38200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>49400</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4422,65 +4558,68 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>115100</v>
+      </c>
+      <c r="E60" s="3">
         <v>113900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>103600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>100800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>95200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>101900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>107500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>101700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>93700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>88900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>103200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>95600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>101300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>96400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>90800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>96800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>91800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>101600</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4502,65 +4641,68 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>548300</v>
+      </c>
+      <c r="E61" s="3">
         <v>561300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>578700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>578800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>577300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>576700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>575100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>585400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>603100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>629500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>654000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>662900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>643600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>635600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>636800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>636300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>637700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>570400</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4582,65 +4724,68 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E62" s="3">
         <v>6500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>13100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>88800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>106800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>148800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>176100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>159100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>144900</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4656,14 +4801,17 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4742,8 +4890,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4822,8 +4973,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4902,65 +5056,68 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>715000</v>
+      </c>
+      <c r="E66" s="3">
         <v>725400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>720400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>719600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>712200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>725500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>734900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>746800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>762200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>781200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>815300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>821900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>833700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>838800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>876400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>909200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>888600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>816900</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4982,8 +5139,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5012,8 +5172,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5092,8 +5253,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5172,8 +5336,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5252,8 +5419,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5332,65 +5502,68 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>63900</v>
+      </c>
+      <c r="E72" s="3">
         <v>57600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>58400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>47600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>44700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>82500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>88800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>71700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>68000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>66800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>66000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>53000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>48800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>64000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>32400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-8100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-25000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-7000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5412,8 +5585,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5492,8 +5668,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5572,8 +5751,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5652,65 +5834,68 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>448900</v>
+      </c>
+      <c r="E76" s="3">
         <v>439700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>437800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>424600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>421200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>458700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>463200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>444900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>441200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>437900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>435400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>420400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>416000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>418300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>384400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>339400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>304500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>319800</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5732,8 +5917,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5812,82 +6000,85 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45928</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45837</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45746</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45564</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45200</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45109</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45018</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44836</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44745</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44654</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44374</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44283</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43918</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5897,77 +6088,80 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-37800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>13000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-15200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>31600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>40600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>16900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-18000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-30200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>23100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4900</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5977,8 +6171,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6007,79 +6204,80 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E83" s="3">
         <v>3500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>6400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>5700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4700</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
@@ -6087,8 +6285,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6167,8 +6368,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6247,8 +6451,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6327,8 +6534,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6407,8 +6617,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6487,77 +6700,80 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E89" s="3">
         <v>7400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>40500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>25700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>18800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>31200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>22500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>30700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>18300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-3300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-21500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>27400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>19000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>12800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>17600</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6567,8 +6783,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6597,79 +6816,80 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-1700</v>
       </c>
       <c r="M91" s="3">
         <v>-1700</v>
       </c>
       <c r="N91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="O91" s="3">
         <v>-1000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -6677,8 +6897,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6757,8 +6980,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6837,79 +7063,82 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>4700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-16200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-62200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-57800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-158900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1300</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -6917,8 +7146,11 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6947,8 +7179,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6985,8 +7218,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7027,8 +7260,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7107,8 +7343,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7187,8 +7426,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7267,77 +7509,80 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-15000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-12400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-17700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-26000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-27400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-8400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>8300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>47900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>30800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>163000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>27500</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7347,13 +7592,16 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -7362,44 +7610,44 @@
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7412,8 +7660,8 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -7427,77 +7675,80 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-13100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>24800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12000</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>4200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>21900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>9500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>7800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-17600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-31800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>15800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>16900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>43800</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7505,6 +7756,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HLLY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="92">
   <si>
     <t>HLLY</t>
   </si>
@@ -656,114 +656,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45928</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45837</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45746</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45564</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45200</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45109</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45018</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44836</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44745</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44654</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44374</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44283</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43918</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
@@ -773,163 +774,169 @@
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>147300</v>
+      </c>
+      <c r="E8" s="3">
         <v>155400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>138400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>166700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>153000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>140100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>134000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>169500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>158600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>155700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>156500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>175300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>172200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>154200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>154800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>179400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>200100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>179800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>159700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>193000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>160300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>138400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>107200</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>86600</v>
+      </c>
+      <c r="E9" s="3">
         <v>82700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>78500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>97100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>89000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>68000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>81700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>99200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>106600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>95500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>98200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>105500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>104500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>106900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>106400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>104100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>117300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>105100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>94500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>111800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>94700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>83900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>63800</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
@@ -939,80 +946,83 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E10" s="3">
         <v>72800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>59800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>69600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>64100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>72100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>52300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>70300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>52100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>60300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>58400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>69700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>67700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>47300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>48400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>75300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>82800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>74700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>65200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>81200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>65600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>54500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>43400</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1022,8 +1032,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1053,80 +1066,81 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E12" s="3">
         <v>4900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>6100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>6200</v>
-      </c>
-      <c r="O12" s="3">
-        <v>6700</v>
       </c>
       <c r="P12" s="3">
         <v>6700</v>
       </c>
       <c r="Q12" s="3">
+        <v>6700</v>
+      </c>
+      <c r="R12" s="3">
         <v>6000</v>
-      </c>
-      <c r="R12" s="3">
-        <v>8200</v>
       </c>
       <c r="S12" s="3">
         <v>8200</v>
       </c>
       <c r="T12" s="3">
+        <v>8200</v>
+      </c>
+      <c r="U12" s="3">
         <v>8100</v>
-      </c>
-      <c r="U12" s="3">
-        <v>7100</v>
       </c>
       <c r="V12" s="3">
         <v>7100</v>
       </c>
       <c r="W12" s="3">
+        <v>7100</v>
+      </c>
+      <c r="X12" s="3">
         <v>6000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6300</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>5600</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1136,8 +1150,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1219,80 +1236,83 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E14" s="3">
         <v>1100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
+        <v>200</v>
+      </c>
+      <c r="I14" s="3">
+        <v>53300</v>
+      </c>
+      <c r="J14" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K14" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="L14" s="3">
+        <v>100</v>
+      </c>
+      <c r="M14" s="3">
+        <v>4400</v>
+      </c>
+      <c r="N14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="P14" s="3">
+        <v>1800</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="R14" s="3">
+        <v>3700</v>
+      </c>
+      <c r="S14" s="3">
+        <v>1700</v>
+      </c>
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
-        <v>53300</v>
-      </c>
-      <c r="I14" s="3">
-        <v>7800</v>
-      </c>
-      <c r="J14" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="K14" s="3">
-        <v>100</v>
-      </c>
-      <c r="L14" s="3">
-        <v>4400</v>
-      </c>
-      <c r="M14" s="3">
-        <v>1100</v>
-      </c>
-      <c r="N14" s="3">
-        <v>1300</v>
-      </c>
-      <c r="O14" s="3">
-        <v>1800</v>
-      </c>
-      <c r="P14" s="3">
-        <v>1300</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>3700</v>
-      </c>
-      <c r="R14" s="3">
-        <v>1700</v>
-      </c>
-      <c r="S14" s="3">
-        <v>300</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>14000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>25000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>4300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>19700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>7500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2300</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1302,8 +1322,11 @@
       <c r="AC14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1311,19 +1334,19 @@
         <v>3400</v>
       </c>
       <c r="E15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F15" s="3">
         <v>3500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3600</v>
-      </c>
-      <c r="I15" s="3">
-        <v>3400</v>
       </c>
       <c r="J15" s="3">
         <v>3400</v>
@@ -1332,10 +1355,10 @@
         <v>3400</v>
       </c>
       <c r="L15" s="3">
+        <v>3400</v>
+      </c>
+      <c r="M15" s="3">
         <v>3500</v>
-      </c>
-      <c r="M15" s="3">
-        <v>3700</v>
       </c>
       <c r="N15" s="3">
         <v>3700</v>
@@ -1356,37 +1379,40 @@
         <v>3700</v>
       </c>
       <c r="T15" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="U15" s="3">
         <v>3600</v>
       </c>
       <c r="V15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="W15" s="3">
         <v>3500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2700</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB15" s="3">
-        <v>0</v>
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1413,80 +1439,81 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>128900</v>
+      </c>
+      <c r="E17" s="3">
         <v>135000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>121100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>138800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>133200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>110500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>120000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>141600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>147800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>136200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>136800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>145000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>144900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>167700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>151700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>154300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>164000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>169300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>159200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>153000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>147600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>125400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>89500</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1496,80 +1523,83 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E18" s="3">
         <v>20500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>17200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>27900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>19800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>29500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>27900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>19700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>30300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>27300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>25100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>36100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>40000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>12700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>13000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>17700</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1579,8 +1609,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1610,68 +1643,69 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3000</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
         <v>5200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>7300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>37600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>27400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-17300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-24200</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1681,8 +1715,8 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
+      <c r="Z20" s="3">
+        <v>0</v>
       </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
@@ -1693,80 +1727,83 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E21" s="3">
         <v>26000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>17700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>31200</v>
       </c>
-      <c r="G21" s="3">
-        <v>23400</v>
-      </c>
       <c r="H21" s="3">
+        <v>23300</v>
+      </c>
+      <c r="I21" s="3">
         <v>27900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>18500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>34700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>17400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>28600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>21400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>32000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>29600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>47200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>58700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>37200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-17200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>45800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>18400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>17900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>22400</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1776,163 +1813,169 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E22" s="3">
         <v>11300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>13500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>15700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>17200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>18800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>18300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>13400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>10400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>9000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>9900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>11200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>10100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>11900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>11500</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E23" s="3">
         <v>9900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>14400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-40500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-7800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>19200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>17100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-19600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>30200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>43600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>24000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-14800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-33500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>28900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>2700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6200</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1942,91 +1985,97 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E24" s="3">
         <v>3600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-3300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1300</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB24" s="3">
-        <v>0</v>
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2108,80 +2157,83 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E26" s="3">
         <v>6300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-37800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-6300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>17100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>13000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>31600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>40600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-18000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-30200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>23100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4900</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2191,80 +2243,83 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E27" s="3">
         <v>6300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-37800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>17100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>13000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>31600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>40600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>16900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-18000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-30200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>23100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4900</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2274,8 +2329,11 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2357,8 +2415,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2440,8 +2501,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2523,8 +2587,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2606,68 +2673,71 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>2000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3000</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
-        <v>100</v>
-      </c>
-      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3">
         <v>-5200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-37600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-27400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>17300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>24200</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -2677,8 +2747,8 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
+      <c r="Z32" s="3">
+        <v>0</v>
       </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
@@ -2689,80 +2759,83 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E33" s="3">
         <v>6300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-37800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>13000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>31600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>40600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>16900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-18000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-30200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>23100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4900</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2772,8 +2845,11 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2855,80 +2931,83 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E35" s="3">
         <v>6300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-37800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>13000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>31600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>40600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>16900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-18000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-30200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>23100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4900</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2938,85 +3017,88 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45928</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45837</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45746</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45564</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45200</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45109</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45018</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44836</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44745</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44654</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44374</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44283</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43918</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3026,8 +3108,11 @@
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3057,8 +3142,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3088,68 +3174,69 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>33100</v>
+      </c>
+      <c r="E41" s="3">
         <v>37200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>50700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>63800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>39100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>56100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>50800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>53100</v>
-      </c>
-      <c r="K41" s="3">
-        <v>41100</v>
       </c>
       <c r="L41" s="3">
         <v>41100</v>
       </c>
       <c r="M41" s="3">
+        <v>41100</v>
+      </c>
+      <c r="N41" s="3">
         <v>36800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>42700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>20800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>26200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>16600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>30600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>44100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>36300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>53900</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3171,8 +3258,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3254,68 +3344,71 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>59100</v>
+      </c>
+      <c r="E43" s="3">
         <v>57900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>49600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>51000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>50900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>36100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>44500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>56100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>48700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>48400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>47400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>57100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>56300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>47100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>59700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>58200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>63700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>51400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>55400</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3331,74 +3424,77 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB43" s="3">
-        <v>0</v>
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>210500</v>
+      </c>
+      <c r="E44" s="3">
         <v>205700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>195700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>180800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>189100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>192500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>179300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>173500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>184000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>192300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>207200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>217500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>229000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>233600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>230500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>214900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>191100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>185000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>164300</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3414,14 +3510,17 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB44" s="3">
-        <v>0</v>
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3440,15 +3539,15 @@
       <c r="H45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>7700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2100</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3461,27 +3560,27 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>18200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>18500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>16900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>15400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>19000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8900</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3503,68 +3602,71 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>317900</v>
+      </c>
+      <c r="E46" s="3">
         <v>316200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>316100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>303200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>288200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>297300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>298600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>301100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>289800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>297400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>304700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>333300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>324200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>325000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>325300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>320500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>314300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>291700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>282600</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3586,8 +3688,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3609,26 +3714,26 @@
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>1200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1100</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>3200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2100</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3660,8 +3765,8 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>3</v>
+      <c r="AA47" s="3">
+        <v>0</v>
       </c>
       <c r="AB47" s="3" t="s">
         <v>3</v>
@@ -3669,68 +3774,71 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E48" s="3">
         <v>78500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>76400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>79000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>76500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>77000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>73600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>73300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>74900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>76500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>78400</v>
-      </c>
-      <c r="N48" s="3">
-        <v>78700</v>
       </c>
       <c r="O48" s="3">
         <v>78700</v>
       </c>
       <c r="P48" s="3">
+        <v>78700</v>
+      </c>
+      <c r="Q48" s="3">
         <v>81700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>86000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>88800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>88000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>51500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>50400</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3746,74 +3854,77 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>771900</v>
+      </c>
+      <c r="E49" s="3">
         <v>769300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>772700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>776100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>779500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>759000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>812000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>822500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>826000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>829500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>832800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>836700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>839400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>843000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>845700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>851500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>846400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>849800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>803700</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3829,14 +3940,17 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3918,8 +4032,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4001,8 +4118,11 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4057,8 +4177,8 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -4084,8 +4204,11 @@
       <c r="AC52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4167,68 +4290,71 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1178800</v>
+      </c>
+      <c r="E54" s="3">
         <v>1164000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1165100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1158200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1144200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1133300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1184200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1198100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1191700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1203300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1219100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1250700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1242300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1249600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1257100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1260800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1248700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1193100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1136700</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4250,8 +4376,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4281,8 +4410,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4312,68 +4442,69 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E57" s="3">
         <v>60100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>51200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>44500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>37600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>44800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>52700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>58600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>50300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>43700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>39800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>43800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>37400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>44900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>43500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>39600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>41900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>45700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>46600</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4389,74 +4520,77 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB57" s="3">
-        <v>0</v>
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E58" s="3">
         <v>12400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>12200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>7000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>6300</v>
       </c>
       <c r="S58" s="3">
         <v>6300</v>
       </c>
       <c r="T58" s="3">
+        <v>6300</v>
+      </c>
+      <c r="U58" s="3">
         <v>7900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5500</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4478,68 +4612,71 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E59" s="3">
         <v>14100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>14900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>49300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>46900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>44900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>48600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>38200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>49400</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4561,68 +4698,71 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E60" s="3">
         <v>115100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>113900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>103600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>100800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>95200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>101900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>107500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>101700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>93700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>88900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>103200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>95600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>101300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>96400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>90800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>96800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>91800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>101600</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4644,68 +4784,71 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>571000</v>
+      </c>
+      <c r="E61" s="3">
         <v>548300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>561300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>578700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>578800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>577300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>576700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>575100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>585400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>603100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>629500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>654000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>662900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>643600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>635600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>636800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>636300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>637700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>570400</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4727,68 +4870,71 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E62" s="3">
         <v>5100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>7300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>88800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>106800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>148800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>176100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>159100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>144900</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4804,14 +4950,17 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4893,8 +5042,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4976,8 +5128,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5059,68 +5214,71 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>722800</v>
+      </c>
+      <c r="E66" s="3">
         <v>715000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>725400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>720400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>719600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>712200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>725500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>734900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>746800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>762200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>781200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>815300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>821900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>833700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>838800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>876400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>909200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>888600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>816900</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5142,8 +5300,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5173,8 +5334,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5256,8 +5418,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5339,8 +5504,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5422,8 +5590,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5505,68 +5676,71 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>71200</v>
+      </c>
+      <c r="E72" s="3">
         <v>63900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>57600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>58400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>47600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>44700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>82500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>88800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>71700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>68000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>66800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>66000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>53000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>48800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>64000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>32400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-8100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-25000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-7000</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5588,8 +5762,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5671,8 +5848,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5754,8 +5934,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5837,68 +6020,71 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>456000</v>
+      </c>
+      <c r="E76" s="3">
         <v>448900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>439700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>437800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>424600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>421200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>458700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>463200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>444900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>441200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>437900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>435400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>420400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>416000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>418300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>384400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>339400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>304500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>319800</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5920,8 +6106,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6003,85 +6192,88 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45928</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45837</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45746</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45564</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45200</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45109</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45018</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44836</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44745</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44654</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44374</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44283</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43918</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6091,80 +6283,83 @@
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E81" s="3">
         <v>6300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-37800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>13000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>31600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>40600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>16900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-18000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-30200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>23100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4900</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6174,8 +6369,11 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6205,82 +6403,83 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E83" s="3">
         <v>4300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>6400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>5600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4700</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -6288,8 +6487,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6371,8 +6573,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6454,8 +6659,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6537,8 +6745,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6620,8 +6831,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6703,80 +6917,83 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E89" s="3">
         <v>6200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>40500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>25700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>18800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>31200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>22500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>30700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-8700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>2500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>18300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-21500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>27400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>19000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>12800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>17600</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6786,8 +7003,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6817,82 +7037,83 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-1700</v>
       </c>
       <c r="N91" s="3">
         <v>-1700</v>
       </c>
       <c r="O91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -6900,8 +7121,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6983,8 +7207,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7066,82 +7293,85 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>4700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-16200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-7200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-62200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-11100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-57800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-158900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1300</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
@@ -7149,8 +7379,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7180,8 +7413,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7221,8 +7455,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7263,8 +7497,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7346,8 +7583,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7429,8 +7669,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7512,80 +7755,83 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-13100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-15000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-12400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-17700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-26000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-27400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-8400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>8300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-3300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>47900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>30800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>163000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>27500</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7595,17 +7841,20 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>900</v>
+      </c>
+      <c r="E101" s="3">
         <v>800</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
@@ -7613,44 +7862,44 @@
         <v>0</v>
       </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7663,8 +7912,8 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z101" s="3">
         <v>0</v>
@@ -7678,80 +7927,83 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-13500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>24800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-17000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>12000</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>4200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>21900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>9500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-13500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>7800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-17600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-31800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>15800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>16900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>43800</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7759,6 +8011,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
